--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127083824</v>
       </c>
       <c r="B19" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>127084313</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127083760</v>
+        <v>127085991</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3407,7 +3407,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591943</v>
+        <v>591906</v>
       </c>
       <c r="R26" t="n">
-        <v>6985251</v>
+        <v>6985404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,7 +3483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127085991</v>
+        <v>127083760</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3514,7 +3514,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591906</v>
+        <v>591943</v>
       </c>
       <c r="R27" t="n">
-        <v>6985404</v>
+        <v>6985251</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,7 +3593,7 @@
         <v>127083875</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>91337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,17 +3951,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3988,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127103022</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>91263</v>
+        <v>97314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591867</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985156</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
         <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127103024</v>
+        <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91263</v>
+        <v>91615</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591804</v>
+        <v>591855</v>
       </c>
       <c r="R38" t="n">
-        <v>6985247</v>
+        <v>6985379</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127103026</v>
+        <v>127102949</v>
       </c>
       <c r="B39" t="n">
-        <v>91263</v>
+        <v>91319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591854</v>
+        <v>591853</v>
       </c>
       <c r="R39" t="n">
-        <v>6985257</v>
+        <v>6985380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102985</v>
+        <v>127103026</v>
       </c>
       <c r="B40" t="n">
-        <v>91541</v>
+        <v>91337</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591855</v>
+        <v>591854</v>
       </c>
       <c r="R40" t="n">
-        <v>6985379</v>
+        <v>6985257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102949</v>
+        <v>127103024</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>91337</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591853</v>
+        <v>591804</v>
       </c>
       <c r="R41" t="n">
-        <v>6985380</v>
+        <v>6985247</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,7 +4966,7 @@
         <v>127102992</v>
       </c>
       <c r="B42" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127102970</v>
+        <v>127102954</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591819</v>
+        <v>591777</v>
       </c>
       <c r="R44" t="n">
-        <v>6985229</v>
+        <v>6985164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102967</v>
+        <v>127102970</v>
       </c>
       <c r="B45" t="n">
         <v>57657</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591885</v>
+        <v>591819</v>
       </c>
       <c r="R45" t="n">
-        <v>6985050</v>
+        <v>6985229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102954</v>
+        <v>127102967</v>
       </c>
       <c r="B46" t="n">
         <v>57657</v>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591777</v>
+        <v>591885</v>
       </c>
       <c r="R46" t="n">
-        <v>6985164</v>
+        <v>6985050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5573,7 +5573,7 @@
         <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102966</v>
+        <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>80142</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591971</v>
+        <v>591936</v>
       </c>
       <c r="R50" t="n">
-        <v>6985052</v>
+        <v>6985363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5840,11 +5840,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5871,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102990</v>
+        <v>127102966</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5906,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591936</v>
+        <v>591971</v>
       </c>
       <c r="R51" t="n">
-        <v>6985363</v>
+        <v>6985052</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5942,6 +5937,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5971,7 +5971,7 @@
         <v>127102984</v>
       </c>
       <c r="B52" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127103011</v>
+        <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80083</v>
+        <v>80142</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591848</v>
+        <v>591892</v>
       </c>
       <c r="R53" t="n">
-        <v>6985246</v>
+        <v>6985312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127103012</v>
+        <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>591973</v>
+        <v>591848</v>
       </c>
       <c r="R54" t="n">
-        <v>6985271</v>
+        <v>6985246</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127102991</v>
+        <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>80114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>591892</v>
+        <v>591973</v>
       </c>
       <c r="R55" t="n">
-        <v>6985312</v>
+        <v>6985271</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91605</v>
+        <v>91679</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127083824</v>
       </c>
       <c r="B19" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>91339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R23" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B24" t="n">
-        <v>91333</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R24" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
         <v>127084313</v>
       </c>
       <c r="B25" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127085991</v>
+        <v>127083760</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3407,7 +3407,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591906</v>
+        <v>591943</v>
       </c>
       <c r="R26" t="n">
-        <v>6985404</v>
+        <v>6985251</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,7 +3483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127083760</v>
+        <v>127085991</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3514,7 +3514,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591943</v>
+        <v>591906</v>
       </c>
       <c r="R27" t="n">
-        <v>6985251</v>
+        <v>6985404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,7 +3593,7 @@
         <v>127083875</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103022</v>
+        <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>91337</v>
+        <v>97320</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591867</v>
+        <v>591866</v>
       </c>
       <c r="R31" t="n">
-        <v>6985156</v>
+        <v>6985352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>91343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4080,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>97314</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,32 +4182,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127102981</v>
+        <v>127103013</v>
       </c>
       <c r="B34" t="n">
-        <v>80018</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591847</v>
+        <v>592025</v>
       </c>
       <c r="R34" t="n">
-        <v>6985209</v>
+        <v>6985242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127103013</v>
+        <v>127102981</v>
       </c>
       <c r="B35" t="n">
-        <v>80114</v>
+        <v>80021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592025</v>
+        <v>591847</v>
       </c>
       <c r="R35" t="n">
-        <v>6985242</v>
+        <v>6985209</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127102949</v>
       </c>
       <c r="B39" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>127103026</v>
       </c>
       <c r="B40" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>127103024</v>
       </c>
       <c r="B41" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127102992</v>
+        <v>127102972</v>
       </c>
       <c r="B42" t="n">
-        <v>80142</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591987</v>
+        <v>591924</v>
       </c>
       <c r="R42" t="n">
-        <v>6985280</v>
+        <v>6985382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,6 +5034,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,32 +5065,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127102972</v>
+        <v>127102992</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5095,10 +5100,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591924</v>
+        <v>591987</v>
       </c>
       <c r="R43" t="n">
-        <v>6985382</v>
+        <v>6985280</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5131,11 +5136,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5162,7 +5162,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127102954</v>
+        <v>127102970</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591777</v>
+        <v>591819</v>
       </c>
       <c r="R44" t="n">
-        <v>6985164</v>
+        <v>6985229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102970</v>
+        <v>127102954</v>
       </c>
       <c r="B45" t="n">
         <v>57657</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591819</v>
+        <v>591777</v>
       </c>
       <c r="R45" t="n">
-        <v>6985229</v>
+        <v>6985164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5573,7 +5573,7 @@
         <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>127102984</v>
       </c>
       <c r="B52" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127102991</v>
+        <v>127103012</v>
       </c>
       <c r="B53" t="n">
-        <v>80142</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591892</v>
+        <v>591973</v>
       </c>
       <c r="R53" t="n">
-        <v>6985312</v>
+        <v>6985271</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6165,7 +6165,7 @@
         <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127103012</v>
+        <v>127102991</v>
       </c>
       <c r="B55" t="n">
-        <v>80114</v>
+        <v>80145</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>591973</v>
+        <v>591892</v>
       </c>
       <c r="R55" t="n">
-        <v>6985271</v>
+        <v>6985312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91679</v>
+        <v>91685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,34 +2892,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R21" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,39 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R22" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,11 +3059,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R23" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R24" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>97320</v>
+        <v>91343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>91343</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,32 +4182,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127103013</v>
+        <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592025</v>
+        <v>591847</v>
       </c>
       <c r="R34" t="n">
-        <v>6985242</v>
+        <v>6985209</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127102981</v>
+        <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80021</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591847</v>
+        <v>592025</v>
       </c>
       <c r="R35" t="n">
-        <v>6985209</v>
+        <v>6985242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103026</v>
+        <v>127103024</v>
       </c>
       <c r="B40" t="n">
         <v>91343</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591854</v>
+        <v>591804</v>
       </c>
       <c r="R40" t="n">
-        <v>6985257</v>
+        <v>6985247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103024</v>
+        <v>127103026</v>
       </c>
       <c r="B41" t="n">
         <v>91343</v>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591804</v>
+        <v>591854</v>
       </c>
       <c r="R41" t="n">
-        <v>6985247</v>
+        <v>6985257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127102972</v>
+        <v>127102992</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591924</v>
+        <v>591987</v>
       </c>
       <c r="R42" t="n">
-        <v>6985382</v>
+        <v>6985280</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,11 +5034,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,32 +5060,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127102992</v>
+        <v>127102972</v>
       </c>
       <c r="B43" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591987</v>
+        <v>591924</v>
       </c>
       <c r="R43" t="n">
-        <v>6985280</v>
+        <v>6985382</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,6 +5131,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>80145</v>
+        <v>91779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R50" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102966</v>
+        <v>127102990</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591971</v>
+        <v>591936</v>
       </c>
       <c r="R51" t="n">
-        <v>6985052</v>
+        <v>6985363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,11 +5937,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,32 +5963,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127102984</v>
+        <v>127102966</v>
       </c>
       <c r="B52" t="n">
-        <v>91779</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591859</v>
+        <v>591971</v>
       </c>
       <c r="R52" t="n">
-        <v>6985376</v>
+        <v>6985052</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6039,6 +6034,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6065,32 +6065,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127103012</v>
+        <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>80145</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591973</v>
+        <v>591892</v>
       </c>
       <c r="R53" t="n">
-        <v>6985271</v>
+        <v>6985312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127102991</v>
+        <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80145</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>591892</v>
+        <v>591973</v>
       </c>
       <c r="R55" t="n">
-        <v>6985312</v>
+        <v>6985271</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,39 +2892,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R21" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,34 +2989,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R22" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3983,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4080,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B48" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R48" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,12 +5635,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,10 +5672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5678,21 +5683,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R49" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,17 +5737,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,34 +2892,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R21" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,39 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R22" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,11 +3059,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,7 +3185,7 @@
         <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>91339</v>
+        <v>91340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B31" t="n">
-        <v>91343</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R31" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,12 +3951,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3986,7 +3991,7 @@
         <v>127102989</v>
       </c>
       <c r="B32" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,10 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4091,21 +4096,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4578,7 +4578,7 @@
         <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127102949</v>
+        <v>127103024</v>
       </c>
       <c r="B39" t="n">
-        <v>91325</v>
+        <v>91344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591853</v>
+        <v>591804</v>
       </c>
       <c r="R39" t="n">
-        <v>6985380</v>
+        <v>6985247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B40" t="n">
-        <v>91343</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R40" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,7 +4869,7 @@
         <v>127103026</v>
       </c>
       <c r="B41" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R48" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,17 +5635,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5683,21 +5678,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R49" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5737,12 +5732,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>91779</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R50" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B51" t="n">
-        <v>80145</v>
+        <v>91780</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R51" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91685</v>
+        <v>91686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,39 +2892,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R21" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,34 +2989,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R22" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>91340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R23" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B24" t="n">
-        <v>91340</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R24" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,17 +3951,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3988,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>97321</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127103022</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>91344</v>
+        <v>97321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591867</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985156</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>80145</v>
+        <v>91780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R50" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102984</v>
+        <v>127102966</v>
       </c>
       <c r="B51" t="n">
-        <v>91780</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591859</v>
+        <v>591971</v>
       </c>
       <c r="R51" t="n">
-        <v>6985376</v>
+        <v>6985052</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,6 +5937,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5963,32 +5968,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127102966</v>
+        <v>127102990</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591971</v>
+        <v>591936</v>
       </c>
       <c r="R52" t="n">
-        <v>6985052</v>
+        <v>6985363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,11 +6039,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,34 +2892,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R21" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,39 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R22" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,11 +3059,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3376,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127083760</v>
+        <v>127085991</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3407,7 +3407,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591943</v>
+        <v>591906</v>
       </c>
       <c r="R26" t="n">
-        <v>6985251</v>
+        <v>6985404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,7 +3483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127085991</v>
+        <v>127083760</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3514,7 +3514,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591906</v>
+        <v>591943</v>
       </c>
       <c r="R27" t="n">
-        <v>6985404</v>
+        <v>6985251</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127102985</v>
+        <v>127103024</v>
       </c>
       <c r="B38" t="n">
-        <v>91622</v>
+        <v>91344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591855</v>
+        <v>591804</v>
       </c>
       <c r="R38" t="n">
-        <v>6985379</v>
+        <v>6985247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127103024</v>
+        <v>127103026</v>
       </c>
       <c r="B39" t="n">
         <v>91344</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591804</v>
+        <v>591854</v>
       </c>
       <c r="R39" t="n">
-        <v>6985247</v>
+        <v>6985257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R40" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103026</v>
+        <v>127102949</v>
       </c>
       <c r="B41" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591854</v>
+        <v>591853</v>
       </c>
       <c r="R41" t="n">
-        <v>6985257</v>
+        <v>6985380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102954</v>
+        <v>127102967</v>
       </c>
       <c r="B45" t="n">
         <v>57657</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591777</v>
+        <v>591885</v>
       </c>
       <c r="R45" t="n">
-        <v>6985164</v>
+        <v>6985050</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102967</v>
+        <v>127102954</v>
       </c>
       <c r="B46" t="n">
         <v>57657</v>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591885</v>
+        <v>591777</v>
       </c>
       <c r="R46" t="n">
-        <v>6985050</v>
+        <v>6985164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>91780</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R50" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102966</v>
+        <v>127102984</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>91780</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591971</v>
+        <v>591859</v>
       </c>
       <c r="R51" t="n">
-        <v>6985052</v>
+        <v>6985376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,11 +5937,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,32 +5963,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127102990</v>
+        <v>127102966</v>
       </c>
       <c r="B52" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591936</v>
+        <v>591971</v>
       </c>
       <c r="R52" t="n">
-        <v>6985363</v>
+        <v>6985052</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6039,6 +6034,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,39 +2892,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R21" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,34 +2989,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R22" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102985</v>
+        <v>127102949</v>
       </c>
       <c r="B40" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591855</v>
+        <v>591853</v>
       </c>
       <c r="R40" t="n">
-        <v>6985379</v>
+        <v>6985380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R41" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6848,6 +6848,2414 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127465982</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>591776</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6985152</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127465993</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>591924</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6985051</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127465989</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>591799</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6985325</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127465983</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>591948</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6985043</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127466001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>591855</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6985260</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127465988</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>591800</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6985244</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127466002</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>591847</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6985306</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127465991</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97321</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>591810</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6985305</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127466000</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>591915</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6985079</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127465987</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>591806</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6985224</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127466003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>591856</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6985302</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127465999</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>591801</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6985241</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127465986</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>591909</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6985075</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127465998</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91340</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>591839</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6985308</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127466008</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>591849</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6985307</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127465994</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>591870</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6985348</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127466005</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>591871</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6985199</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127466013</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>591844</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6985189</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127465985</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>591950</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6984943</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127466007</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>591874</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6985297</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127466006</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>591829</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6985195</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127466004</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>591826</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6985300</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127465981</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>591791</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6985305</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127465984</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>591879</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6985046</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,34 +2892,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R21" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,39 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R22" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,11 +3059,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>91340</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R23" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R24" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R40" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102985</v>
+        <v>127102949</v>
       </c>
       <c r="B41" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591855</v>
+        <v>591853</v>
       </c>
       <c r="R41" t="n">
-        <v>6985379</v>
+        <v>6985380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127083824</v>
       </c>
       <c r="B19" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>127084313</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127085991</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>127083760</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>127083875</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>127102971</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127102968</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127103024</v>
+        <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591804</v>
+        <v>591855</v>
       </c>
       <c r="R38" t="n">
-        <v>6985247</v>
+        <v>6985379</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127103026</v>
+        <v>127102949</v>
       </c>
       <c r="B39" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591854</v>
+        <v>591853</v>
       </c>
       <c r="R39" t="n">
-        <v>6985257</v>
+        <v>6985380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102985</v>
+        <v>127103024</v>
       </c>
       <c r="B40" t="n">
-        <v>91622</v>
+        <v>91348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591855</v>
+        <v>591804</v>
       </c>
       <c r="R40" t="n">
-        <v>6985379</v>
+        <v>6985247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102949</v>
+        <v>127103026</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591853</v>
+        <v>591854</v>
       </c>
       <c r="R41" t="n">
-        <v>6985380</v>
+        <v>6985257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,7 +4966,7 @@
         <v>127102992</v>
       </c>
       <c r="B42" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>127102972</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>127102970</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102967</v>
+        <v>127102954</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591885</v>
+        <v>591777</v>
       </c>
       <c r="R45" t="n">
-        <v>6985050</v>
+        <v>6985164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102954</v>
+        <v>127102967</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591777</v>
+        <v>591885</v>
       </c>
       <c r="R46" t="n">
-        <v>6985164</v>
+        <v>6985050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5471,7 +5471,7 @@
         <v>127102953</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>80145</v>
+        <v>91784</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R50" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B51" t="n">
-        <v>91780</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R51" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
         <v>127102966</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>127102969</v>
       </c>
       <c r="B57" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91686</v>
+        <v>91690</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465982</v>
+        <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>80121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,39 +6861,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591776</v>
+        <v>591924</v>
       </c>
       <c r="R61" t="n">
-        <v>6985152</v>
+        <v>6985051</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6926,11 +6921,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6957,10 +6947,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465993</v>
+        <v>127465982</v>
       </c>
       <c r="B62" t="n">
-        <v>80117</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6968,34 +6958,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591924</v>
+        <v>591776</v>
       </c>
       <c r="R62" t="n">
-        <v>6985051</v>
+        <v>6985152</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7028,6 +7023,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7057,7 +7057,7 @@
         <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>127465983</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>127465988</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>127465987</v>
       </c>
       <c r="B70" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466008</v>
+        <v>127466005</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591849</v>
+        <v>591871</v>
       </c>
       <c r="R75" t="n">
-        <v>6985307</v>
+        <v>6985199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B76" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R76" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466005</v>
+        <v>127465994</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,21 +8473,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591871</v>
+        <v>591870</v>
       </c>
       <c r="R77" t="n">
-        <v>6985199</v>
+        <v>6985348</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,45 +8559,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B78" t="n">
-        <v>98347</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R78" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8630,6 +8635,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8656,50 +8666,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>57657</v>
+        <v>98351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8732,11 +8737,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8766,7 +8766,7 @@
         <v>127466007</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>127466006</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>127465984</v>
       </c>
       <c r="B84" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,39 +2892,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R21" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,34 +2989,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R22" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3376,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127085991</v>
+        <v>127083760</v>
       </c>
       <c r="B26" t="n">
         <v>57661</v>
@@ -3407,7 +3407,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591906</v>
+        <v>591943</v>
       </c>
       <c r="R26" t="n">
-        <v>6985404</v>
+        <v>6985251</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,7 +3483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127083760</v>
+        <v>127085991</v>
       </c>
       <c r="B27" t="n">
         <v>57661</v>
@@ -3514,7 +3514,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591943</v>
+        <v>591906</v>
       </c>
       <c r="R27" t="n">
-        <v>6985251</v>
+        <v>6985404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103022</v>
+        <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>97325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591867</v>
+        <v>591866</v>
       </c>
       <c r="R31" t="n">
-        <v>6985156</v>
+        <v>6985352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4080,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127102949</v>
+        <v>127103024</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591853</v>
+        <v>591804</v>
       </c>
       <c r="R39" t="n">
-        <v>6985380</v>
+        <v>6985247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103024</v>
+        <v>127103026</v>
       </c>
       <c r="B40" t="n">
         <v>91348</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591804</v>
+        <v>591854</v>
       </c>
       <c r="R40" t="n">
-        <v>6985247</v>
+        <v>6985257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103026</v>
+        <v>127102949</v>
       </c>
       <c r="B41" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591854</v>
+        <v>591853</v>
       </c>
       <c r="R41" t="n">
-        <v>6985257</v>
+        <v>6985380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R48" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,12 +5635,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,10 +5672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5678,21 +5683,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R49" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,17 +5737,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>91784</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R50" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R51" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465993</v>
+        <v>127465982</v>
       </c>
       <c r="B61" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,34 +6861,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591924</v>
+        <v>591776</v>
       </c>
       <c r="R61" t="n">
-        <v>6985051</v>
+        <v>6985152</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6921,6 +6926,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6947,7 +6957,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465982</v>
+        <v>127465989</v>
       </c>
       <c r="B62" t="n">
         <v>57661</v>
@@ -6978,7 +6988,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591776</v>
+        <v>591799</v>
       </c>
       <c r="R62" t="n">
-        <v>6985152</v>
+        <v>6985325</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7027,7 +7037,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,10 +7064,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465989</v>
+        <v>127465993</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7065,39 +7075,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591799</v>
+        <v>591924</v>
       </c>
       <c r="R63" t="n">
-        <v>6985325</v>
+        <v>6985051</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7130,11 +7135,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8268,32 +8268,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466005</v>
+        <v>127466013</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>98351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591871</v>
+        <v>591844</v>
       </c>
       <c r="R75" t="n">
-        <v>6985199</v>
+        <v>6985189</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466008</v>
+        <v>127466005</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591849</v>
+        <v>591871</v>
       </c>
       <c r="R76" t="n">
-        <v>6985307</v>
+        <v>6985199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B77" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,21 +8473,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R77" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,10 +8559,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465985</v>
+        <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8570,39 +8570,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591950</v>
+        <v>591870</v>
       </c>
       <c r="R78" t="n">
-        <v>6984943</v>
+        <v>6985348</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8635,11 +8630,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8666,45 +8656,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B79" t="n">
-        <v>98351</v>
+        <v>57661</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8737,6 +8732,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>91344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R23" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B24" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R24" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>97325</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R48" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,17 +5635,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5683,21 +5678,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R49" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5737,12 +5732,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465982</v>
+        <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,39 +6861,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591776</v>
+        <v>591924</v>
       </c>
       <c r="R61" t="n">
-        <v>6985152</v>
+        <v>6985051</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6926,11 +6921,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6957,7 +6947,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465989</v>
+        <v>127465982</v>
       </c>
       <c r="B62" t="n">
         <v>57661</v>
@@ -6988,7 +6978,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591799</v>
+        <v>591776</v>
       </c>
       <c r="R62" t="n">
-        <v>6985325</v>
+        <v>6985152</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7037,7 +7027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7064,10 +7054,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465993</v>
+        <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7075,34 +7065,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591924</v>
+        <v>591799</v>
       </c>
       <c r="R63" t="n">
-        <v>6985051</v>
+        <v>6985325</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7135,6 +7130,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3983,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4080,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,32 +4182,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127102981</v>
+        <v>127103013</v>
       </c>
       <c r="B34" t="n">
-        <v>80025</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591847</v>
+        <v>592025</v>
       </c>
       <c r="R34" t="n">
-        <v>6985209</v>
+        <v>6985242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127103013</v>
+        <v>127102981</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80025</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592025</v>
+        <v>591847</v>
       </c>
       <c r="R35" t="n">
-        <v>6985242</v>
+        <v>6985209</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103026</v>
+        <v>127102949</v>
       </c>
       <c r="B40" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591854</v>
+        <v>591853</v>
       </c>
       <c r="R40" t="n">
-        <v>6985257</v>
+        <v>6985380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102949</v>
+        <v>127103026</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591853</v>
+        <v>591854</v>
       </c>
       <c r="R41" t="n">
-        <v>6985380</v>
+        <v>6985257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -8268,32 +8268,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466013</v>
+        <v>127466005</v>
       </c>
       <c r="B75" t="n">
-        <v>98351</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591844</v>
+        <v>591871</v>
       </c>
       <c r="R75" t="n">
-        <v>6985189</v>
+        <v>6985199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466005</v>
+        <v>127466008</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591871</v>
+        <v>591849</v>
       </c>
       <c r="R76" t="n">
-        <v>6985199</v>
+        <v>6985307</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466008</v>
+        <v>127465994</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,21 +8473,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591849</v>
+        <v>591870</v>
       </c>
       <c r="R77" t="n">
-        <v>6985307</v>
+        <v>6985348</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,10 +8559,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465994</v>
+        <v>127465985</v>
       </c>
       <c r="B78" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8570,34 +8570,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591870</v>
+        <v>591950</v>
       </c>
       <c r="R78" t="n">
-        <v>6985348</v>
+        <v>6984943</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8630,6 +8635,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8656,50 +8666,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>57661</v>
+        <v>98352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8732,11 +8737,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3983,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,32 +4182,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127103013</v>
+        <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>80025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592025</v>
+        <v>591847</v>
       </c>
       <c r="R34" t="n">
-        <v>6985242</v>
+        <v>6985209</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127102981</v>
+        <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80025</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591847</v>
+        <v>592025</v>
       </c>
       <c r="R35" t="n">
-        <v>6985209</v>
+        <v>6985242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127102992</v>
+        <v>127102972</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591987</v>
+        <v>591924</v>
       </c>
       <c r="R42" t="n">
-        <v>6985280</v>
+        <v>6985382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,6 +5034,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,32 +5065,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127102972</v>
+        <v>127102992</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5095,10 +5100,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591924</v>
+        <v>591987</v>
       </c>
       <c r="R43" t="n">
-        <v>6985382</v>
+        <v>6985280</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5131,11 +5136,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127083824</v>
       </c>
       <c r="B19" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127087699</v>
       </c>
       <c r="B23" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127085735</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>127084313</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127083760</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>127085991</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>127083875</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>127102971</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R31" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,12 +3951,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,32 +3988,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>97327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4053,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
         <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127102968</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B39" t="n">
-        <v>91348</v>
+        <v>91332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R39" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102949</v>
+        <v>127103026</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591853</v>
+        <v>591854</v>
       </c>
       <c r="R40" t="n">
-        <v>6985380</v>
+        <v>6985257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103026</v>
+        <v>127103024</v>
       </c>
       <c r="B41" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591854</v>
+        <v>591804</v>
       </c>
       <c r="R41" t="n">
-        <v>6985257</v>
+        <v>6985247</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,7 +4966,7 @@
         <v>127102972</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>127102992</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>127102970</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102954</v>
+        <v>127102967</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591777</v>
+        <v>591885</v>
       </c>
       <c r="R45" t="n">
-        <v>6985164</v>
+        <v>6985050</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102967</v>
+        <v>127102954</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591885</v>
+        <v>591777</v>
       </c>
       <c r="R46" t="n">
-        <v>6985050</v>
+        <v>6985164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5471,7 +5471,7 @@
         <v>127102953</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R48" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,12 +5635,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,10 +5672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5678,21 +5683,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R49" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,17 +5737,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102990</v>
+        <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>91786</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591936</v>
+        <v>591859</v>
       </c>
       <c r="R50" t="n">
-        <v>6985363</v>
+        <v>6985376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B51" t="n">
-        <v>91784</v>
+        <v>80151</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R51" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
         <v>127102966</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>127102969</v>
       </c>
       <c r="B57" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>127465982</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>127465983</v>
       </c>
       <c r="B64" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>127465988</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>127465987</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127466003</v>
+        <v>127465986</v>
       </c>
       <c r="B71" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,34 +7881,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>591856</v>
+        <v>591909</v>
       </c>
       <c r="R71" t="n">
-        <v>6985302</v>
+        <v>6985075</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7941,6 +7946,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7967,10 +7977,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127465999</v>
+        <v>127466003</v>
       </c>
       <c r="B72" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8002,10 +8012,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591801</v>
+        <v>591856</v>
       </c>
       <c r="R72" t="n">
-        <v>6985241</v>
+        <v>6985302</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8064,10 +8074,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465986</v>
+        <v>127465999</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8075,39 +8085,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591909</v>
+        <v>591801</v>
       </c>
       <c r="R73" t="n">
-        <v>6985075</v>
+        <v>6985241</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8140,11 +8145,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466005</v>
+        <v>127465994</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591871</v>
+        <v>591870</v>
       </c>
       <c r="R75" t="n">
-        <v>6985199</v>
+        <v>6985348</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,32 +8365,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466008</v>
+        <v>127466013</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>98354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591849</v>
+        <v>591844</v>
       </c>
       <c r="R76" t="n">
-        <v>6985307</v>
+        <v>6985189</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465994</v>
+        <v>127465985</v>
       </c>
       <c r="B77" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,34 +8473,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591870</v>
+        <v>591950</v>
       </c>
       <c r="R77" t="n">
-        <v>6985348</v>
+        <v>6984943</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8533,6 +8538,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8559,10 +8569,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465985</v>
+        <v>127466005</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8570,39 +8580,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591950</v>
+        <v>591871</v>
       </c>
       <c r="R78" t="n">
-        <v>6984943</v>
+        <v>6985199</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8635,11 +8640,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8666,32 +8666,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127466008</v>
       </c>
       <c r="B79" t="n">
-        <v>98352</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591849</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6985307</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8766,7 +8766,7 @@
         <v>127466007</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>127466006</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>127465984</v>
       </c>
       <c r="B84" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R31" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,17 +3951,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3988,32 +3983,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>97327</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R32" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4085,10 +4080,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4096,21 +4091,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127102949</v>
+        <v>127103024</v>
       </c>
       <c r="B39" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591853</v>
+        <v>591804</v>
       </c>
       <c r="R39" t="n">
-        <v>6985380</v>
+        <v>6985247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R41" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127102972</v>
+        <v>127102992</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>80151</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591924</v>
+        <v>591987</v>
       </c>
       <c r="R42" t="n">
-        <v>6985382</v>
+        <v>6985280</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,11 +5034,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,32 +5060,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127102992</v>
+        <v>127102972</v>
       </c>
       <c r="B43" t="n">
-        <v>80151</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591987</v>
+        <v>591924</v>
       </c>
       <c r="R43" t="n">
-        <v>6985280</v>
+        <v>6985382</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,6 +5131,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102967</v>
+        <v>127102954</v>
       </c>
       <c r="B45" t="n">
         <v>57663</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591885</v>
+        <v>591777</v>
       </c>
       <c r="R45" t="n">
-        <v>6985050</v>
+        <v>6985164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102954</v>
+        <v>127102967</v>
       </c>
       <c r="B46" t="n">
         <v>57663</v>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591777</v>
+        <v>591885</v>
       </c>
       <c r="R46" t="n">
-        <v>6985164</v>
+        <v>6985050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R48" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,17 +5635,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5683,21 +5678,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R49" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5737,12 +5732,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B75" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R75" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,32 +8365,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466013</v>
+        <v>127466005</v>
       </c>
       <c r="B76" t="n">
-        <v>98354</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591844</v>
+        <v>591871</v>
       </c>
       <c r="R76" t="n">
-        <v>6985189</v>
+        <v>6985199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466005</v>
+        <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591871</v>
+        <v>591870</v>
       </c>
       <c r="R78" t="n">
-        <v>6985199</v>
+        <v>6985348</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,32 +8666,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466008</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>98354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591849</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6985307</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>97327</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R39" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103026</v>
+        <v>127103024</v>
       </c>
       <c r="B40" t="n">
         <v>91350</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591854</v>
+        <v>591804</v>
       </c>
       <c r="R40" t="n">
-        <v>6985257</v>
+        <v>6985247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102949</v>
+        <v>127103026</v>
       </c>
       <c r="B41" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591853</v>
+        <v>591854</v>
       </c>
       <c r="R41" t="n">
-        <v>6985380</v>
+        <v>6985257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103022</v>
+        <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>97327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591867</v>
+        <v>591866</v>
       </c>
       <c r="R31" t="n">
-        <v>6985156</v>
+        <v>6985352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127102955</v>
+        <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591771</v>
+        <v>591867</v>
       </c>
       <c r="R32" t="n">
-        <v>6985164</v>
+        <v>6985156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,32 +4080,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102989</v>
+        <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591866</v>
+        <v>591771</v>
       </c>
       <c r="R33" t="n">
-        <v>6985352</v>
+        <v>6985164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,12 +4145,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127102985</v>
+        <v>127103024</v>
       </c>
       <c r="B38" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591855</v>
+        <v>591804</v>
       </c>
       <c r="R38" t="n">
-        <v>6985379</v>
+        <v>6985247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103024</v>
+        <v>127103026</v>
       </c>
       <c r="B40" t="n">
         <v>91350</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591804</v>
+        <v>591854</v>
       </c>
       <c r="R40" t="n">
-        <v>6985247</v>
+        <v>6985257</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103026</v>
+        <v>127102985</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591854</v>
+        <v>591855</v>
       </c>
       <c r="R41" t="n">
-        <v>6985257</v>
+        <v>6985379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B48" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R48" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,12 +5635,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,10 +5672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5678,21 +5683,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R49" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,17 +5737,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -8268,7 +8268,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466008</v>
+        <v>127466005</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591849</v>
+        <v>591871</v>
       </c>
       <c r="R75" t="n">
-        <v>6985307</v>
+        <v>6985199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466005</v>
+        <v>127465994</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591871</v>
+        <v>591870</v>
       </c>
       <c r="R76" t="n">
-        <v>6985199</v>
+        <v>6985348</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,50 +8462,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B77" t="n">
-        <v>57663</v>
+        <v>98354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R77" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8538,11 +8533,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8569,10 +8559,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B78" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8580,21 +8570,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R78" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,45 +8656,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B79" t="n">
-        <v>98354</v>
+        <v>57663</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8737,6 +8732,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B21" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,34 +2892,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R21" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,39 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R22" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,11 +3059,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127087699</v>
+        <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3096,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591856</v>
+        <v>591940</v>
       </c>
       <c r="R23" t="n">
-        <v>6985238</v>
+        <v>6985373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127085735</v>
+        <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591940</v>
+        <v>591856</v>
       </c>
       <c r="R24" t="n">
-        <v>6985373</v>
+        <v>6985238</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B38" t="n">
-        <v>91350</v>
+        <v>91338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R38" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B39" t="n">
-        <v>91332</v>
+        <v>91634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R39" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103026</v>
+        <v>127103024</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591854</v>
+        <v>591804</v>
       </c>
       <c r="R40" t="n">
-        <v>6985257</v>
+        <v>6985247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127102985</v>
+        <v>127103026</v>
       </c>
       <c r="B41" t="n">
-        <v>91628</v>
+        <v>91356</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591855</v>
+        <v>591854</v>
       </c>
       <c r="R41" t="n">
-        <v>6985379</v>
+        <v>6985257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127102952</v>
+        <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5581,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591799</v>
+        <v>592037</v>
       </c>
       <c r="R48" t="n">
-        <v>6985112</v>
+        <v>6985242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,17 +5635,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127102951</v>
+        <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5683,21 +5678,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592037</v>
+        <v>591799</v>
       </c>
       <c r="R49" t="n">
-        <v>6985242</v>
+        <v>6985112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5737,12 +5732,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5772,7 +5772,7 @@
         <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91692</v>
+        <v>91698</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465993</v>
+        <v>127465982</v>
       </c>
       <c r="B61" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,34 +6861,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591924</v>
+        <v>591776</v>
       </c>
       <c r="R61" t="n">
-        <v>6985051</v>
+        <v>6985152</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6921,6 +6926,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6947,7 +6957,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465982</v>
+        <v>127465989</v>
       </c>
       <c r="B62" t="n">
         <v>57663</v>
@@ -6978,7 +6988,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591776</v>
+        <v>591799</v>
       </c>
       <c r="R62" t="n">
-        <v>6985152</v>
+        <v>6985325</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7027,7 +7037,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,10 +7064,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465989</v>
+        <v>127465993</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7065,39 +7075,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591799</v>
+        <v>591924</v>
       </c>
       <c r="R63" t="n">
-        <v>6985325</v>
+        <v>6985051</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7130,11 +7135,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127465986</v>
+        <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,39 +7881,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>591909</v>
+        <v>591856</v>
       </c>
       <c r="R71" t="n">
-        <v>6985075</v>
+        <v>6985302</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7946,11 +7941,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7977,10 +7967,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127466003</v>
+        <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8012,10 +8002,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591856</v>
+        <v>591801</v>
       </c>
       <c r="R72" t="n">
-        <v>6985302</v>
+        <v>6985241</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8074,10 +8064,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465999</v>
+        <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8085,34 +8075,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591801</v>
+        <v>591909</v>
       </c>
       <c r="R73" t="n">
-        <v>6985241</v>
+        <v>6985075</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8145,6 +8140,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B76" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R76" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,32 +8462,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466013</v>
+        <v>127465994</v>
       </c>
       <c r="B77" t="n">
-        <v>98354</v>
+        <v>80123</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591844</v>
+        <v>591870</v>
       </c>
       <c r="R77" t="n">
-        <v>6985189</v>
+        <v>6985348</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,32 +8559,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466008</v>
+        <v>127466013</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591849</v>
+        <v>591844</v>
       </c>
       <c r="R78" t="n">
-        <v>6985307</v>
+        <v>6985189</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127083824</v>
       </c>
       <c r="B19" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127085680</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127084034</v>
+        <v>127083839</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>80126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,39 +2892,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591927</v>
+        <v>591918</v>
       </c>
       <c r="R21" t="n">
-        <v>6985197</v>
+        <v>6985244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127083839</v>
+        <v>127084034</v>
       </c>
       <c r="B22" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,34 +2989,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591918</v>
+        <v>591927</v>
       </c>
       <c r="R22" t="n">
-        <v>6985244</v>
+        <v>6985197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,7 +3088,7 @@
         <v>127085735</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127087699</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>127084313</v>
       </c>
       <c r="B25" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127083760</v>
+        <v>127085991</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591943</v>
+        <v>591906</v>
       </c>
       <c r="R26" t="n">
-        <v>6985251</v>
+        <v>6985404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,10 +3483,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127085991</v>
+        <v>127083760</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591906</v>
+        <v>591943</v>
       </c>
       <c r="R27" t="n">
-        <v>6985404</v>
+        <v>6985251</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,7 +3593,7 @@
         <v>127083875</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>127102971</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127102989</v>
       </c>
       <c r="B31" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127103022</v>
       </c>
       <c r="B32" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>127102955</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127102968</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B38" t="n">
-        <v>91338</v>
+        <v>91637</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R38" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127102985</v>
+        <v>127103026</v>
       </c>
       <c r="B39" t="n">
-        <v>91634</v>
+        <v>91359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591855</v>
+        <v>591854</v>
       </c>
       <c r="R39" t="n">
-        <v>6985379</v>
+        <v>6985257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B40" t="n">
-        <v>91356</v>
+        <v>91341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R40" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103026</v>
+        <v>127103024</v>
       </c>
       <c r="B41" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591854</v>
+        <v>591804</v>
       </c>
       <c r="R41" t="n">
-        <v>6985257</v>
+        <v>6985247</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127102992</v>
+        <v>127102972</v>
       </c>
       <c r="B42" t="n">
-        <v>80151</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591987</v>
+        <v>591924</v>
       </c>
       <c r="R42" t="n">
-        <v>6985280</v>
+        <v>6985382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,6 +5034,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,32 +5065,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127102972</v>
+        <v>127102992</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>80154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5095,10 +5100,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591924</v>
+        <v>591987</v>
       </c>
       <c r="R43" t="n">
-        <v>6985382</v>
+        <v>6985280</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5131,11 +5136,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127102970</v>
+        <v>127102967</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591819</v>
+        <v>591885</v>
       </c>
       <c r="R44" t="n">
-        <v>6985229</v>
+        <v>6985050</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102954</v>
+        <v>127102970</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591777</v>
+        <v>591819</v>
       </c>
       <c r="R45" t="n">
-        <v>6985164</v>
+        <v>6985229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127102967</v>
+        <v>127102954</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591885</v>
+        <v>591777</v>
       </c>
       <c r="R46" t="n">
-        <v>6985050</v>
+        <v>6985164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5471,7 +5471,7 @@
         <v>127102953</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>127102984</v>
       </c>
       <c r="B50" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102990</v>
+        <v>127102966</v>
       </c>
       <c r="B51" t="n">
-        <v>80151</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591936</v>
+        <v>591971</v>
       </c>
       <c r="R51" t="n">
-        <v>6985363</v>
+        <v>6985052</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,6 +5937,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5963,32 +5968,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127102966</v>
+        <v>127102990</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>80154</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591971</v>
+        <v>591936</v>
       </c>
       <c r="R52" t="n">
-        <v>6985052</v>
+        <v>6985363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,11 +6039,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6068,7 +6068,7 @@
         <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>127102969</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465982</v>
+        <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>57663</v>
+        <v>80126</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,39 +6861,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591776</v>
+        <v>591924</v>
       </c>
       <c r="R61" t="n">
-        <v>6985152</v>
+        <v>6985051</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6926,11 +6921,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6957,10 +6947,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465989</v>
+        <v>127465982</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6988,7 +6978,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591799</v>
+        <v>591776</v>
       </c>
       <c r="R62" t="n">
-        <v>6985325</v>
+        <v>6985152</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7037,7 +7027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7064,10 +7054,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465993</v>
+        <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7075,34 +7065,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591924</v>
+        <v>591799</v>
       </c>
       <c r="R63" t="n">
-        <v>6985051</v>
+        <v>6985325</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7135,6 +7130,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7164,7 +7164,7 @@
         <v>127465983</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>127465988</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>127465987</v>
       </c>
       <c r="B70" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,32 +8268,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466005</v>
+        <v>127466013</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>98363</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591871</v>
+        <v>591844</v>
       </c>
       <c r="R75" t="n">
-        <v>6985199</v>
+        <v>6985189</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466008</v>
+        <v>127466005</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591849</v>
+        <v>591871</v>
       </c>
       <c r="R76" t="n">
-        <v>6985307</v>
+        <v>6985199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B77" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,21 +8473,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R77" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,32 +8559,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466013</v>
+        <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>80126</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591844</v>
+        <v>591870</v>
       </c>
       <c r="R78" t="n">
-        <v>6985189</v>
+        <v>6985348</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8659,7 +8659,7 @@
         <v>127465985</v>
       </c>
       <c r="B79" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>127466007</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>127466006</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9054,45 +9054,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127465981</v>
+        <v>127465984</v>
       </c>
       <c r="B83" t="n">
-        <v>91303</v>
+        <v>57666</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>591791</v>
+        <v>591879</v>
       </c>
       <c r="R83" t="n">
-        <v>6985305</v>
+        <v>6985046</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9125,6 +9130,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9151,50 +9161,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127465984</v>
+        <v>127465981</v>
       </c>
       <c r="B84" t="n">
-        <v>57663</v>
+        <v>91306</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>591879</v>
+        <v>591791</v>
       </c>
       <c r="R84" t="n">
-        <v>6985046</v>
+        <v>6985305</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9227,11 +9232,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -3690,7 +3690,7 @@
         <v>127102986</v>
       </c>
       <c r="B29" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>127102971</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,32 +3886,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127102989</v>
+        <v>127103022</v>
       </c>
       <c r="B31" t="n">
-        <v>97336</v>
+        <v>91367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591866</v>
+        <v>591867</v>
       </c>
       <c r="R31" t="n">
-        <v>6985352</v>
+        <v>6985156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127103022</v>
+        <v>127102955</v>
       </c>
       <c r="B32" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591867</v>
+        <v>591771</v>
       </c>
       <c r="R32" t="n">
-        <v>6985156</v>
+        <v>6985164</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4048,12 +4048,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,32 +4085,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127102955</v>
+        <v>127102989</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>97344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591771</v>
+        <v>591866</v>
       </c>
       <c r="R33" t="n">
-        <v>6985164</v>
+        <v>6985352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,17 +4150,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4185,7 +4185,7 @@
         <v>127102981</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>127103013</v>
       </c>
       <c r="B35" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>127103010</v>
       </c>
       <c r="B36" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127102968</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127102985</v>
+        <v>127103024</v>
       </c>
       <c r="B38" t="n">
-        <v>91637</v>
+        <v>91367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591855</v>
+        <v>591804</v>
       </c>
       <c r="R38" t="n">
-        <v>6985379</v>
+        <v>6985247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,7 +4675,7 @@
         <v>127103026</v>
       </c>
       <c r="B39" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127102949</v>
+        <v>127102985</v>
       </c>
       <c r="B40" t="n">
-        <v>91341</v>
+        <v>91645</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591853</v>
+        <v>591855</v>
       </c>
       <c r="R40" t="n">
-        <v>6985380</v>
+        <v>6985379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127103024</v>
+        <v>127102949</v>
       </c>
       <c r="B41" t="n">
-        <v>91359</v>
+        <v>91349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591804</v>
+        <v>591853</v>
       </c>
       <c r="R41" t="n">
-        <v>6985247</v>
+        <v>6985380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,7 +4966,7 @@
         <v>127102972</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>127102992</v>
       </c>
       <c r="B43" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127102967</v>
+        <v>127102970</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591885</v>
+        <v>591819</v>
       </c>
       <c r="R44" t="n">
-        <v>6985050</v>
+        <v>6985229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127102970</v>
+        <v>127102967</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591819</v>
+        <v>591885</v>
       </c>
       <c r="R45" t="n">
-        <v>6985229</v>
+        <v>6985050</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5369,7 +5369,7 @@
         <v>127102954</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>127102953</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>127102951</v>
       </c>
       <c r="B48" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127102952</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,32 +5769,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127102984</v>
+        <v>127102990</v>
       </c>
       <c r="B50" t="n">
-        <v>91795</v>
+        <v>80160</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591859</v>
+        <v>591936</v>
       </c>
       <c r="R50" t="n">
-        <v>6985376</v>
+        <v>6985363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,32 +5866,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127102966</v>
+        <v>127102984</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>91803</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591971</v>
+        <v>591859</v>
       </c>
       <c r="R51" t="n">
-        <v>6985052</v>
+        <v>6985376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,11 +5937,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,32 +5963,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127102990</v>
+        <v>127102966</v>
       </c>
       <c r="B52" t="n">
-        <v>80154</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591936</v>
+        <v>591971</v>
       </c>
       <c r="R52" t="n">
-        <v>6985363</v>
+        <v>6985052</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6039,6 +6034,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6068,7 +6068,7 @@
         <v>127102991</v>
       </c>
       <c r="B53" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>127103011</v>
       </c>
       <c r="B54" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>127103012</v>
       </c>
       <c r="B55" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>127102980</v>
       </c>
       <c r="B56" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>127102969</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127102950</v>
       </c>
       <c r="B58" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>127103006</v>
       </c>
       <c r="B59" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91701</v>
+        <v>91709</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>127465982</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>127465983</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>127465988</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>127465987</v>
       </c>
       <c r="B70" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,45 +8268,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B75" t="n">
-        <v>98363</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R75" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8339,6 +8344,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8368,7 +8378,7 @@
         <v>127466005</v>
       </c>
       <c r="B76" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8465,7 +8475,7 @@
         <v>127466008</v>
       </c>
       <c r="B77" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,7 +8572,7 @@
         <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8656,50 +8666,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>57666</v>
+        <v>98371</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8732,11 +8737,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8766,7 +8766,7 @@
         <v>127466007</v>
       </c>
       <c r="B80" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>127466006</v>
       </c>
       <c r="B81" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9054,50 +9054,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127465984</v>
+        <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>57666</v>
+        <v>91314</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>591879</v>
+        <v>591791</v>
       </c>
       <c r="R83" t="n">
-        <v>6985046</v>
+        <v>6985305</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9130,11 +9125,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9161,45 +9151,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127465981</v>
+        <v>127465984</v>
       </c>
       <c r="B84" t="n">
-        <v>91306</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>591791</v>
+        <v>591879</v>
       </c>
       <c r="R84" t="n">
-        <v>6985305</v>
+        <v>6985046</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9232,6 +9227,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -6752,7 +6752,7 @@
         <v>127168974</v>
       </c>
       <c r="B60" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7967,10 +7967,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127465999</v>
+        <v>127465986</v>
       </c>
       <c r="B72" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7978,34 +7978,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591801</v>
+        <v>591909</v>
       </c>
       <c r="R72" t="n">
-        <v>6985241</v>
+        <v>6985075</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8038,6 +8043,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8064,10 +8074,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465986</v>
+        <v>127465999</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8075,39 +8085,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591909</v>
+        <v>591801</v>
       </c>
       <c r="R73" t="n">
-        <v>6985075</v>
+        <v>6985241</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8140,11 +8145,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127465985</v>
+        <v>127466008</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,39 +8279,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591950</v>
+        <v>591849</v>
       </c>
       <c r="R75" t="n">
-        <v>6984943</v>
+        <v>6985307</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8344,11 +8339,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8375,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466005</v>
+        <v>127465994</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8386,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8410,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591871</v>
+        <v>591870</v>
       </c>
       <c r="R76" t="n">
-        <v>6985199</v>
+        <v>6985348</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8472,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466008</v>
+        <v>127465985</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8483,34 +8473,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591849</v>
+        <v>591950</v>
       </c>
       <c r="R77" t="n">
-        <v>6985307</v>
+        <v>6984943</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8543,6 +8538,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8569,32 +8569,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465994</v>
+        <v>127466013</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>98372</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591870</v>
+        <v>591844</v>
       </c>
       <c r="R78" t="n">
-        <v>6985348</v>
+        <v>6985189</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,32 +8666,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127466005</v>
       </c>
       <c r="B79" t="n">
-        <v>98371</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591871</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6985199</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -7967,10 +7967,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127465986</v>
+        <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7978,39 +7978,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591909</v>
+        <v>591801</v>
       </c>
       <c r="R72" t="n">
-        <v>6985075</v>
+        <v>6985241</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8043,11 +8038,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8074,10 +8064,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465999</v>
+        <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8085,34 +8075,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591801</v>
+        <v>591909</v>
       </c>
       <c r="R73" t="n">
-        <v>6985241</v>
+        <v>6985075</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8145,6 +8140,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466008</v>
+        <v>127465994</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591849</v>
+        <v>591870</v>
       </c>
       <c r="R75" t="n">
-        <v>6985307</v>
+        <v>6985348</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127465994</v>
+        <v>127465985</v>
       </c>
       <c r="B76" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,34 +8376,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591870</v>
+        <v>591950</v>
       </c>
       <c r="R76" t="n">
-        <v>6985348</v>
+        <v>6984943</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8436,6 +8441,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8462,10 +8472,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465985</v>
+        <v>127466005</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,39 +8483,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591950</v>
+        <v>591871</v>
       </c>
       <c r="R77" t="n">
-        <v>6984943</v>
+        <v>6985199</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8538,11 +8543,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8569,32 +8569,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466013</v>
+        <v>127466008</v>
       </c>
       <c r="B78" t="n">
-        <v>98372</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591844</v>
+        <v>591849</v>
       </c>
       <c r="R78" t="n">
-        <v>6985189</v>
+        <v>6985307</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,32 +8666,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466005</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>98372</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591871</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6985199</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9054,45 +9054,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127465981</v>
+        <v>127465984</v>
       </c>
       <c r="B83" t="n">
-        <v>91315</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>591791</v>
+        <v>591879</v>
       </c>
       <c r="R83" t="n">
-        <v>6985305</v>
+        <v>6985046</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9125,6 +9130,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9151,50 +9161,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127465984</v>
+        <v>127465981</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>91315</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>591879</v>
+        <v>591791</v>
       </c>
       <c r="R84" t="n">
-        <v>6985046</v>
+        <v>6985305</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9227,11 +9232,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465993</v>
+        <v>127465982</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,34 +6861,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591924</v>
+        <v>591776</v>
       </c>
       <c r="R61" t="n">
-        <v>6985051</v>
+        <v>6985152</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6921,6 +6926,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6947,7 +6957,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465982</v>
+        <v>127465989</v>
       </c>
       <c r="B62" t="n">
         <v>57672</v>
@@ -6978,7 +6988,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591776</v>
+        <v>591799</v>
       </c>
       <c r="R62" t="n">
-        <v>6985152</v>
+        <v>6985325</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7027,7 +7037,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,10 +7064,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465989</v>
+        <v>127465993</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7065,39 +7075,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591799</v>
+        <v>591924</v>
       </c>
       <c r="R63" t="n">
-        <v>6985325</v>
+        <v>6985051</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7130,11 +7135,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127466003</v>
+        <v>127465986</v>
       </c>
       <c r="B71" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,34 +7881,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>591856</v>
+        <v>591909</v>
       </c>
       <c r="R71" t="n">
-        <v>6985302</v>
+        <v>6985075</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7941,6 +7946,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7967,10 +7977,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127465999</v>
+        <v>127466003</v>
       </c>
       <c r="B72" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8002,10 +8012,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591801</v>
+        <v>591856</v>
       </c>
       <c r="R72" t="n">
-        <v>6985241</v>
+        <v>6985302</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8064,10 +8074,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465986</v>
+        <v>127465999</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8075,39 +8085,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591909</v>
+        <v>591801</v>
       </c>
       <c r="R73" t="n">
-        <v>6985075</v>
+        <v>6985241</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8140,11 +8145,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8268,32 +8268,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127465994</v>
+        <v>127466013</v>
       </c>
       <c r="B75" t="n">
-        <v>80132</v>
+        <v>98373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591870</v>
+        <v>591844</v>
       </c>
       <c r="R75" t="n">
-        <v>6985348</v>
+        <v>6985189</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127465985</v>
+        <v>127466005</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,39 +8376,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591950</v>
+        <v>591871</v>
       </c>
       <c r="R76" t="n">
-        <v>6984943</v>
+        <v>6985199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8441,11 +8436,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8472,7 +8462,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466005</v>
+        <v>127466008</v>
       </c>
       <c r="B77" t="n">
         <v>79029</v>
@@ -8507,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591871</v>
+        <v>591849</v>
       </c>
       <c r="R77" t="n">
-        <v>6985199</v>
+        <v>6985307</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8569,10 +8559,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466008</v>
+        <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8580,21 +8570,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591849</v>
+        <v>591870</v>
       </c>
       <c r="R78" t="n">
-        <v>6985307</v>
+        <v>6985348</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,45 +8656,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B79" t="n">
-        <v>98372</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8737,6 +8732,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9054,50 +9054,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127465984</v>
+        <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>91316</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>591879</v>
+        <v>591791</v>
       </c>
       <c r="R83" t="n">
-        <v>6985046</v>
+        <v>6985305</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9130,11 +9125,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9161,45 +9151,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127465981</v>
+        <v>127465984</v>
       </c>
       <c r="B84" t="n">
-        <v>91315</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>591791</v>
+        <v>591879</v>
       </c>
       <c r="R84" t="n">
-        <v>6985305</v>
+        <v>6985046</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9232,6 +9227,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465982</v>
+        <v>127465993</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,39 +6861,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591776</v>
+        <v>591924</v>
       </c>
       <c r="R61" t="n">
-        <v>6985152</v>
+        <v>6985051</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6926,11 +6921,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6957,7 +6947,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465989</v>
+        <v>127465982</v>
       </c>
       <c r="B62" t="n">
         <v>57672</v>
@@ -6988,7 +6978,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591799</v>
+        <v>591776</v>
       </c>
       <c r="R62" t="n">
-        <v>6985325</v>
+        <v>6985152</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7037,7 +7027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7064,10 +7054,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465993</v>
+        <v>127465989</v>
       </c>
       <c r="B63" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7075,34 +7065,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591924</v>
+        <v>591799</v>
       </c>
       <c r="R63" t="n">
-        <v>6985051</v>
+        <v>6985325</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7135,6 +7130,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7271,7 +7271,7 @@
         <v>127466001</v>
       </c>
       <c r="B65" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>127466002</v>
       </c>
       <c r="B67" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>127465991</v>
       </c>
       <c r="B68" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>127466000</v>
       </c>
       <c r="B69" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127465986</v>
+        <v>127466003</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,39 +7881,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>591909</v>
+        <v>591856</v>
       </c>
       <c r="R71" t="n">
-        <v>6985075</v>
+        <v>6985302</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7946,11 +7941,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7977,10 +7967,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127466003</v>
+        <v>127465999</v>
       </c>
       <c r="B72" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8012,10 +8002,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>591856</v>
+        <v>591801</v>
       </c>
       <c r="R72" t="n">
-        <v>6985302</v>
+        <v>6985241</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8074,10 +8064,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127465999</v>
+        <v>127465986</v>
       </c>
       <c r="B73" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8085,34 +8075,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>591801</v>
+        <v>591909</v>
       </c>
       <c r="R73" t="n">
-        <v>6985241</v>
+        <v>6985075</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8145,6 +8140,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre bohål, ca 2m upp i gran m granticka. Stammen knäckt i höjd m bohålet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8174,7 +8174,7 @@
         <v>127465998</v>
       </c>
       <c r="B74" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>127466013</v>
       </c>
       <c r="B75" t="n">
-        <v>98373</v>
+        <v>98374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>127466004</v>
       </c>
       <c r="B82" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127465981</v>
       </c>
       <c r="B83" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -6850,10 +6850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127465993</v>
+        <v>127465982</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6861,34 +6861,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>591924</v>
+        <v>591776</v>
       </c>
       <c r="R61" t="n">
-        <v>6985051</v>
+        <v>6985152</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6921,6 +6926,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6947,7 +6957,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127465982</v>
+        <v>127465989</v>
       </c>
       <c r="B62" t="n">
         <v>57672</v>
@@ -6978,7 +6988,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>591776</v>
+        <v>591799</v>
       </c>
       <c r="R62" t="n">
-        <v>6985152</v>
+        <v>6985325</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7027,7 +7037,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7054,10 +7064,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127465989</v>
+        <v>127465993</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7065,39 +7075,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>591799</v>
+        <v>591924</v>
       </c>
       <c r="R63" t="n">
-        <v>6985325</v>
+        <v>6985051</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7130,11 +7135,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bohål, 2m upp i granhögstubbe, bohål ca 4 cm diameter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8268,45 +8268,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B75" t="n">
-        <v>98374</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R75" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8339,6 +8344,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8656,50 +8666,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>98374</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8732,11 +8737,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,45 +9054,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127465981</v>
+        <v>127465984</v>
       </c>
       <c r="B83" t="n">
-        <v>91317</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>591791</v>
+        <v>591879</v>
       </c>
       <c r="R83" t="n">
-        <v>6985305</v>
+        <v>6985046</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9125,6 +9130,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9151,50 +9161,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127465984</v>
+        <v>127465981</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>591879</v>
+        <v>591791</v>
       </c>
       <c r="R84" t="n">
-        <v>6985046</v>
+        <v>6985305</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9227,11 +9232,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127465985</v>
+        <v>127466005</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,39 +8279,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591950</v>
+        <v>591871</v>
       </c>
       <c r="R75" t="n">
-        <v>6984943</v>
+        <v>6985199</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8344,11 +8339,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8375,7 +8365,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466005</v>
+        <v>127466008</v>
       </c>
       <c r="B76" t="n">
         <v>79029</v>
@@ -8410,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591871</v>
+        <v>591849</v>
       </c>
       <c r="R76" t="n">
-        <v>6985199</v>
+        <v>6985307</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8472,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127466008</v>
+        <v>127465994</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8483,21 +8473,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8507,10 +8497,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591849</v>
+        <v>591870</v>
       </c>
       <c r="R77" t="n">
-        <v>6985307</v>
+        <v>6985348</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8569,32 +8559,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127465994</v>
+        <v>127466013</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>98374</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591870</v>
+        <v>591844</v>
       </c>
       <c r="R78" t="n">
-        <v>6985348</v>
+        <v>6985189</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8666,45 +8656,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127466013</v>
+        <v>127465985</v>
       </c>
       <c r="B79" t="n">
-        <v>98374</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591844</v>
+        <v>591950</v>
       </c>
       <c r="R79" t="n">
-        <v>6985189</v>
+        <v>6984943</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8737,6 +8732,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -8268,10 +8268,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127466005</v>
+        <v>127465985</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,34 +8279,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>591871</v>
+        <v>591950</v>
       </c>
       <c r="R75" t="n">
-        <v>6985199</v>
+        <v>6984943</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8339,6 +8344,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8365,7 +8375,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127466008</v>
+        <v>127466005</v>
       </c>
       <c r="B76" t="n">
         <v>79029</v>
@@ -8400,10 +8410,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>591849</v>
+        <v>591871</v>
       </c>
       <c r="R76" t="n">
-        <v>6985307</v>
+        <v>6985199</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8462,10 +8472,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127465994</v>
+        <v>127466008</v>
       </c>
       <c r="B77" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,21 +8483,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8497,10 +8507,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>591870</v>
+        <v>591849</v>
       </c>
       <c r="R77" t="n">
-        <v>6985348</v>
+        <v>6985307</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8559,32 +8569,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127466013</v>
+        <v>127465994</v>
       </c>
       <c r="B78" t="n">
-        <v>98374</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8594,10 +8604,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>591844</v>
+        <v>591870</v>
       </c>
       <c r="R78" t="n">
-        <v>6985189</v>
+        <v>6985348</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8656,50 +8666,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127465985</v>
+        <v>127466013</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>98374</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>591950</v>
+        <v>591844</v>
       </c>
       <c r="R79" t="n">
-        <v>6984943</v>
+        <v>6985189</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8732,11 +8737,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9256,6 +9256,3396 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129431351</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>591924</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6985247</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129431350</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>591921</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6985249</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129431295</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>591845</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6985340</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129431307</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>591866</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6985144</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129431297</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>591797</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6985276</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129431301</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>591768</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6985170</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129431352</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>591869</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6985147</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129431292</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>591779</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6985266</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129431335</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>591938</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6985274</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129431341</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>591829</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6985164</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129431300</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>591764</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6985160</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129431303</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>591852</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6985216</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129431340</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>591826</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6985197</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129431347</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>591979</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6985182</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129431345</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>591986</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6985193</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129431349</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>591958</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6985180</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129431346</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>592009</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6985158</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129431296</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>591811</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6985350</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129431304</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>591804</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6985177</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129431294</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>591828</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6985311</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129431299</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>591817</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6985225</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129431354</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>591920</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6985069</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129431338</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>591805</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6985202</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129431336</v>
+      </c>
+      <c r="B108" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>591851</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6985252</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129431344</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>592011</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6985171</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129431337</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>591849</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6985248</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129431302</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>591830</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6985205</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129431348</v>
+      </c>
+      <c r="B112" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>591980</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6985185</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129431353</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>591892</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6985085</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129431293</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>591777</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6985297</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129431355</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>591975</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6985013</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129431334</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92138</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>760</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>592005</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6985296</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129431298</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>591793</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6985264</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129431339</v>
+      </c>
+      <c r="B118" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>591807</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6985203</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9261,7 +9261,7 @@
         <v>129431351</v>
       </c>
       <c r="B85" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>129431350</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>129431352</v>
       </c>
       <c r="B91" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431292</v>
+        <v>129431335</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,39 +9975,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591779</v>
+        <v>591938</v>
       </c>
       <c r="R92" t="n">
-        <v>6985266</v>
+        <v>6985274</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10034,12 +10029,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10066,10 +10061,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431335</v>
+        <v>129431292</v>
       </c>
       <c r="B93" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10077,34 +10072,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591938</v>
+        <v>591779</v>
       </c>
       <c r="R93" t="n">
-        <v>6985274</v>
+        <v>6985266</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10131,12 +10131,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10163,10 +10163,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431341</v>
+        <v>129431300</v>
       </c>
       <c r="B94" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10174,30 +10174,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591829</v>
+        <v>591764</v>
       </c>
       <c r="R94" t="n">
-        <v>6985164</v>
+        <v>6985160</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10224,12 +10236,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10256,7 +10273,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431300</v>
+        <v>129431303</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10285,24 +10302,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591764</v>
+        <v>591852</v>
       </c>
       <c r="R95" t="n">
-        <v>6985160</v>
+        <v>6985216</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10329,17 +10343,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10366,10 +10375,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431303</v>
+        <v>129431341</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10377,39 +10386,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591852</v>
+        <v>591829</v>
       </c>
       <c r="R96" t="n">
-        <v>6985216</v>
+        <v>6985164</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,42 +10479,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R97" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10573,10 +10565,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B98" t="n">
-        <v>80148</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10584,34 +10576,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R98" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B99" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,19 +10681,23 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10701,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R99" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10763,10 +10767,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B100" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10774,23 +10778,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R100" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10863,7 +10863,7 @@
         <v>129431346</v>
       </c>
       <c r="B101" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431299</v>
+        <v>129431354</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,39 +11277,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591817</v>
+        <v>591920</v>
       </c>
       <c r="R105" t="n">
-        <v>6985225</v>
+        <v>6985069</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11336,12 +11331,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11368,32 +11363,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431354</v>
+        <v>129431338</v>
       </c>
       <c r="B106" t="n">
-        <v>80148</v>
+        <v>80178</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11403,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591920</v>
+        <v>591805</v>
       </c>
       <c r="R106" t="n">
-        <v>6985069</v>
+        <v>6985202</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11465,45 +11460,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431338</v>
+        <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591805</v>
+        <v>591817</v>
       </c>
       <c r="R107" t="n">
-        <v>6985202</v>
+        <v>6985225</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11565,7 +11565,7 @@
         <v>129431336</v>
       </c>
       <c r="B108" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B109" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,23 +11670,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11694,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R109" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11756,10 +11752,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B110" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11767,19 +11763,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R110" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11954,7 +11954,7 @@
         <v>129431348</v>
       </c>
       <c r="B112" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>129431353</v>
       </c>
       <c r="B113" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12243,27 +12243,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431355</v>
+        <v>129431298</v>
       </c>
       <c r="B115" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12271,29 +12271,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591975</v>
+        <v>591793</v>
       </c>
       <c r="R115" t="n">
-        <v>6985013</v>
+        <v>6985264</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12320,12 +12313,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12352,45 +12345,57 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431334</v>
+        <v>129431355</v>
       </c>
       <c r="B116" t="n">
-        <v>92138</v>
+        <v>57831</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>592005</v>
+        <v>591975</v>
       </c>
       <c r="R116" t="n">
-        <v>6985296</v>
+        <v>6985013</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12449,50 +12454,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431298</v>
+        <v>129431334</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>92140</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591793</v>
+        <v>592005</v>
       </c>
       <c r="R117" t="n">
-        <v>6985264</v>
+        <v>6985296</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12519,12 +12519,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12554,7 +12554,7 @@
         <v>129431339</v>
       </c>
       <c r="B118" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9874,7 +9874,7 @@
         <v>129431352</v>
       </c>
       <c r="B91" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10061,10 +10061,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431292</v>
+        <v>129431341</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10072,39 +10072,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591779</v>
+        <v>591829</v>
       </c>
       <c r="R93" t="n">
-        <v>6985266</v>
+        <v>6985164</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10131,12 +10122,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10163,7 +10154,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431300</v>
+        <v>129431292</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10192,24 +10183,21 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591764</v>
+        <v>591779</v>
       </c>
       <c r="R94" t="n">
-        <v>6985160</v>
+        <v>6985266</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10242,11 +10230,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10273,7 +10256,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431303</v>
+        <v>129431300</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10302,21 +10285,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591852</v>
+        <v>591764</v>
       </c>
       <c r="R95" t="n">
-        <v>6985216</v>
+        <v>6985160</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10343,12 +10329,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10375,10 +10366,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431341</v>
+        <v>129431303</v>
       </c>
       <c r="B96" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10386,30 +10377,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591829</v>
+        <v>591852</v>
       </c>
       <c r="R96" t="n">
-        <v>6985164</v>
+        <v>6985216</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>91569</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,23 +10681,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10705,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R99" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10767,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B100" t="n">
-        <v>91565</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,19 +10774,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R100" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431354</v>
+        <v>129431299</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,34 +11277,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591920</v>
+        <v>591817</v>
       </c>
       <c r="R105" t="n">
-        <v>6985069</v>
+        <v>6985225</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11331,12 +11336,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11363,32 +11368,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431338</v>
+        <v>129431354</v>
       </c>
       <c r="B106" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11398,10 +11403,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591805</v>
+        <v>591920</v>
       </c>
       <c r="R106" t="n">
-        <v>6985202</v>
+        <v>6985069</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11460,50 +11465,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431299</v>
+        <v>129431338</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591817</v>
+        <v>591805</v>
       </c>
       <c r="R107" t="n">
-        <v>6985225</v>
+        <v>6985202</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B109" t="n">
-        <v>91565</v>
+        <v>80149</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,19 +11670,23 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R109" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11752,10 +11756,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B110" t="n">
-        <v>80149</v>
+        <v>91569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11763,23 +11767,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R110" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11951,34 +11951,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B112" t="n">
-        <v>80178</v>
+        <v>91569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11986,10 +11982,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R112" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12048,30 +12044,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B113" t="n">
-        <v>91565</v>
+        <v>80178</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R113" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12141,10 +12141,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431293</v>
+        <v>129431339</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12152,39 +12152,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591777</v>
+        <v>591807</v>
       </c>
       <c r="R114" t="n">
-        <v>6985297</v>
+        <v>6985203</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12211,12 +12206,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12243,7 +12238,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431298</v>
+        <v>129431293</v>
       </c>
       <c r="B115" t="n">
         <v>57727</v>
@@ -12283,10 +12278,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591793</v>
+        <v>591777</v>
       </c>
       <c r="R115" t="n">
-        <v>6985264</v>
+        <v>6985297</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12345,27 +12340,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431355</v>
+        <v>129431298</v>
       </c>
       <c r="B116" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12373,29 +12368,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591975</v>
+        <v>591793</v>
       </c>
       <c r="R116" t="n">
-        <v>6985013</v>
+        <v>6985264</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12422,12 +12410,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12454,45 +12442,57 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431334</v>
+        <v>129431355</v>
       </c>
       <c r="B117" t="n">
-        <v>92140</v>
+        <v>57831</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>592005</v>
+        <v>591975</v>
       </c>
       <c r="R117" t="n">
-        <v>6985296</v>
+        <v>6985013</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12551,32 +12551,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431339</v>
+        <v>129431334</v>
       </c>
       <c r="B118" t="n">
-        <v>80149</v>
+        <v>92144</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591807</v>
+        <v>592005</v>
       </c>
       <c r="R118" t="n">
-        <v>6985203</v>
+        <v>6985296</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9258,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129431351</v>
+        <v>129431350</v>
       </c>
       <c r="B85" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,21 +9269,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>591924</v>
+        <v>591921</v>
       </c>
       <c r="R85" t="n">
-        <v>6985247</v>
+        <v>6985249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129431350</v>
+        <v>129431351</v>
       </c>
       <c r="B86" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>591921</v>
+        <v>591924</v>
       </c>
       <c r="R86" t="n">
-        <v>6985249</v>
+        <v>6985247</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129431295</v>
+        <v>129431307</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9481,21 +9481,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>591845</v>
+        <v>591866</v>
       </c>
       <c r="R87" t="n">
-        <v>6985340</v>
+        <v>6985144</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9522,12 +9525,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9554,7 +9557,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129431307</v>
+        <v>129431295</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9583,24 +9586,21 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>591866</v>
+        <v>591845</v>
       </c>
       <c r="R88" t="n">
-        <v>6985144</v>
+        <v>6985340</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9874,7 +9874,7 @@
         <v>129431352</v>
       </c>
       <c r="B91" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431335</v>
+        <v>129431292</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,34 +9975,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591938</v>
+        <v>591779</v>
       </c>
       <c r="R92" t="n">
-        <v>6985274</v>
+        <v>6985266</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10029,12 +10034,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10064,7 +10069,7 @@
         <v>129431341</v>
       </c>
       <c r="B93" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10154,10 +10159,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431292</v>
+        <v>129431335</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,39 +10170,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591779</v>
+        <v>591938</v>
       </c>
       <c r="R94" t="n">
-        <v>6985266</v>
+        <v>6985274</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10224,12 +10224,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10256,7 +10256,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431300</v>
+        <v>129431303</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10285,24 +10285,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591764</v>
+        <v>591852</v>
       </c>
       <c r="R95" t="n">
-        <v>6985160</v>
+        <v>6985216</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10329,17 +10326,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10366,7 +10358,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431303</v>
+        <v>129431300</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10395,21 +10387,24 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591852</v>
+        <v>591764</v>
       </c>
       <c r="R96" t="n">
-        <v>6985216</v>
+        <v>6985160</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10436,12 +10431,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B99" t="n">
-        <v>91569</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,19 +10681,23 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10701,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R99" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10763,10 +10767,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B100" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10774,23 +10778,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R100" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431299</v>
+        <v>129431354</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,39 +11277,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591817</v>
+        <v>591920</v>
       </c>
       <c r="R105" t="n">
-        <v>6985225</v>
+        <v>6985069</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11336,12 +11331,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11368,32 +11363,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431354</v>
+        <v>129431338</v>
       </c>
       <c r="B106" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11403,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591920</v>
+        <v>591805</v>
       </c>
       <c r="R106" t="n">
-        <v>6985069</v>
+        <v>6985202</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11465,45 +11460,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431338</v>
+        <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591805</v>
+        <v>591817</v>
       </c>
       <c r="R107" t="n">
-        <v>6985202</v>
+        <v>6985225</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B109" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,23 +11670,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11694,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R109" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11756,10 +11752,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B110" t="n">
-        <v>91569</v>
+        <v>80149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11767,19 +11763,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R110" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11951,30 +11951,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B112" t="n">
-        <v>91569</v>
+        <v>80178</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11982,10 +11986,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R112" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12044,34 +12048,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B113" t="n">
-        <v>80178</v>
+        <v>91570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R113" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12554,7 +12554,7 @@
         <v>129431334</v>
       </c>
       <c r="B118" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9964,7 +9964,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431292</v>
+        <v>129431303</v>
       </c>
       <c r="B92" t="n">
         <v>57727</v>
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591779</v>
+        <v>591852</v>
       </c>
       <c r="R92" t="n">
-        <v>6985266</v>
+        <v>6985216</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10066,10 +10066,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431341</v>
+        <v>129431292</v>
       </c>
       <c r="B93" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10077,30 +10077,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591829</v>
+        <v>591779</v>
       </c>
       <c r="R93" t="n">
-        <v>6985164</v>
+        <v>6985266</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10127,12 +10136,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10159,10 +10168,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431335</v>
+        <v>129431300</v>
       </c>
       <c r="B94" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10170,34 +10179,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591938</v>
+        <v>591764</v>
       </c>
       <c r="R94" t="n">
-        <v>6985274</v>
+        <v>6985160</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10224,12 +10241,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10256,10 +10278,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431303</v>
+        <v>129431341</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10267,39 +10289,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591852</v>
+        <v>591829</v>
       </c>
       <c r="R95" t="n">
-        <v>6985216</v>
+        <v>6985164</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10358,10 +10371,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431300</v>
+        <v>129431335</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10369,42 +10382,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591764</v>
+        <v>591938</v>
       </c>
       <c r="R96" t="n">
-        <v>6985160</v>
+        <v>6985274</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10431,17 +10436,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B97" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,34 +10479,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R97" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10565,10 +10573,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10576,42 +10584,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R98" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,23 +10681,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10705,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R99" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10767,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B100" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,19 +10774,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R100" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431354</v>
+        <v>129431299</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,34 +11277,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591920</v>
+        <v>591817</v>
       </c>
       <c r="R105" t="n">
-        <v>6985069</v>
+        <v>6985225</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11331,12 +11336,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11363,32 +11368,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431338</v>
+        <v>129431354</v>
       </c>
       <c r="B106" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11398,10 +11403,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591805</v>
+        <v>591920</v>
       </c>
       <c r="R106" t="n">
-        <v>6985202</v>
+        <v>6985069</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11460,50 +11465,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431299</v>
+        <v>129431338</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591817</v>
+        <v>591805</v>
       </c>
       <c r="R107" t="n">
-        <v>6985225</v>
+        <v>6985202</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12141,45 +12141,57 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431339</v>
+        <v>129431355</v>
       </c>
       <c r="B114" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591807</v>
+        <v>591975</v>
       </c>
       <c r="R114" t="n">
-        <v>6985203</v>
+        <v>6985013</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12238,50 +12250,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431293</v>
+        <v>129431334</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>92145</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591777</v>
+        <v>592005</v>
       </c>
       <c r="R115" t="n">
-        <v>6985297</v>
+        <v>6985296</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12308,12 +12315,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12340,10 +12347,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431298</v>
+        <v>129431339</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,39 +12358,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591793</v>
+        <v>591807</v>
       </c>
       <c r="R116" t="n">
-        <v>6985264</v>
+        <v>6985203</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12410,12 +12412,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12442,27 +12444,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431355</v>
+        <v>129431298</v>
       </c>
       <c r="B117" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12470,29 +12472,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591975</v>
+        <v>591793</v>
       </c>
       <c r="R117" t="n">
-        <v>6985013</v>
+        <v>6985264</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12519,12 +12514,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12551,45 +12546,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431334</v>
+        <v>129431293</v>
       </c>
       <c r="B118" t="n">
-        <v>92145</v>
+        <v>57727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>592005</v>
+        <v>591777</v>
       </c>
       <c r="R118" t="n">
-        <v>6985296</v>
+        <v>6985297</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12616,12 +12616,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -11059,7 +11059,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129431304</v>
+        <v>129431294</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11088,24 +11088,21 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>591804</v>
+        <v>591828</v>
       </c>
       <c r="R103" t="n">
-        <v>6985177</v>
+        <v>6985311</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11132,12 +11129,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11164,7 +11161,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129431294</v>
+        <v>129431304</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11193,21 +11190,24 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>591828</v>
+        <v>591804</v>
       </c>
       <c r="R104" t="n">
-        <v>6985311</v>
+        <v>6985177</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431299</v>
+        <v>129431354</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,39 +11277,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591817</v>
+        <v>591920</v>
       </c>
       <c r="R105" t="n">
-        <v>6985225</v>
+        <v>6985069</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11336,12 +11331,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11368,32 +11363,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431354</v>
+        <v>129431338</v>
       </c>
       <c r="B106" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11403,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591920</v>
+        <v>591805</v>
       </c>
       <c r="R106" t="n">
-        <v>6985069</v>
+        <v>6985202</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11465,45 +11460,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431338</v>
+        <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591805</v>
+        <v>591817</v>
       </c>
       <c r="R107" t="n">
-        <v>6985202</v>
+        <v>6985225</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B109" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,19 +11670,23 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R109" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11752,10 +11756,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B110" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11763,23 +11767,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R110" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11951,34 +11951,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B112" t="n">
-        <v>80178</v>
+        <v>91570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11986,10 +11982,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R112" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12048,30 +12044,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B113" t="n">
-        <v>91570</v>
+        <v>80178</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R113" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9874,7 +9874,7 @@
         <v>129431352</v>
       </c>
       <c r="B91" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431303</v>
+        <v>129431335</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,39 +9975,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591852</v>
+        <v>591938</v>
       </c>
       <c r="R92" t="n">
-        <v>6985216</v>
+        <v>6985274</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10066,10 +10061,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431292</v>
+        <v>129431341</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10077,39 +10072,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591779</v>
+        <v>591829</v>
       </c>
       <c r="R93" t="n">
-        <v>6985266</v>
+        <v>6985164</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10136,12 +10122,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10168,7 +10154,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431300</v>
+        <v>129431303</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10197,24 +10183,21 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591764</v>
+        <v>591852</v>
       </c>
       <c r="R94" t="n">
-        <v>6985160</v>
+        <v>6985216</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10241,17 +10224,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10278,10 +10256,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431341</v>
+        <v>129431292</v>
       </c>
       <c r="B95" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10289,30 +10267,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591829</v>
+        <v>591779</v>
       </c>
       <c r="R95" t="n">
-        <v>6985164</v>
+        <v>6985266</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10339,12 +10326,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10371,10 +10358,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431335</v>
+        <v>129431300</v>
       </c>
       <c r="B96" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10382,34 +10369,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591938</v>
+        <v>591764</v>
       </c>
       <c r="R96" t="n">
-        <v>6985274</v>
+        <v>6985160</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10436,12 +10431,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10673,7 +10673,7 @@
         <v>129431345</v>
       </c>
       <c r="B99" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129431294</v>
+        <v>129431304</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11088,21 +11088,24 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>591828</v>
+        <v>591804</v>
       </c>
       <c r="R103" t="n">
-        <v>6985311</v>
+        <v>6985177</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11129,12 +11132,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11161,7 +11164,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129431304</v>
+        <v>129431294</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11190,24 +11193,21 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>591804</v>
+        <v>591828</v>
       </c>
       <c r="R104" t="n">
-        <v>6985177</v>
+        <v>6985311</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431354</v>
+        <v>129431299</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,34 +11277,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591920</v>
+        <v>591817</v>
       </c>
       <c r="R105" t="n">
-        <v>6985069</v>
+        <v>6985225</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11331,12 +11336,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11460,10 +11465,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431299</v>
+        <v>129431354</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11471,39 +11476,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591817</v>
+        <v>591920</v>
       </c>
       <c r="R107" t="n">
-        <v>6985225</v>
+        <v>6985069</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B109" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,23 +11670,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11694,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R109" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11756,10 +11752,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B110" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11767,19 +11763,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R110" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11951,30 +11951,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B112" t="n">
-        <v>91570</v>
+        <v>80178</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11982,10 +11986,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R112" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12044,34 +12048,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B113" t="n">
-        <v>80178</v>
+        <v>91573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R113" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12141,57 +12141,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431355</v>
+        <v>129431339</v>
       </c>
       <c r="B114" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591975</v>
+        <v>591807</v>
       </c>
       <c r="R114" t="n">
-        <v>6985013</v>
+        <v>6985203</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12250,45 +12238,57 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431334</v>
+        <v>129431355</v>
       </c>
       <c r="B115" t="n">
-        <v>92145</v>
+        <v>57831</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>592005</v>
+        <v>591975</v>
       </c>
       <c r="R115" t="n">
-        <v>6985296</v>
+        <v>6985013</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12347,32 +12347,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431339</v>
+        <v>129431334</v>
       </c>
       <c r="B116" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12382,10 +12382,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591807</v>
+        <v>592005</v>
       </c>
       <c r="R116" t="n">
-        <v>6985203</v>
+        <v>6985296</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12444,7 +12444,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431298</v>
+        <v>129431293</v>
       </c>
       <c r="B117" t="n">
         <v>57727</v>
@@ -12484,10 +12484,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591793</v>
+        <v>591777</v>
       </c>
       <c r="R117" t="n">
-        <v>6985264</v>
+        <v>6985297</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12546,7 +12546,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431293</v>
+        <v>129431298</v>
       </c>
       <c r="B118" t="n">
         <v>57727</v>
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591777</v>
+        <v>591793</v>
       </c>
       <c r="R118" t="n">
-        <v>6985297</v>
+        <v>6985264</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9452,7 +9452,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129431307</v>
+        <v>129431295</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9481,24 +9481,21 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>591866</v>
+        <v>591845</v>
       </c>
       <c r="R87" t="n">
-        <v>6985144</v>
+        <v>6985340</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9525,12 +9522,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9557,7 +9554,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129431295</v>
+        <v>129431307</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9586,21 +9583,24 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>591845</v>
+        <v>591866</v>
       </c>
       <c r="R88" t="n">
-        <v>6985340</v>
+        <v>6985144</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431335</v>
+        <v>129431341</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,23 +9975,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9999,10 +9995,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591938</v>
+        <v>591829</v>
       </c>
       <c r="R92" t="n">
-        <v>6985274</v>
+        <v>6985164</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10061,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431341</v>
+        <v>129431335</v>
       </c>
       <c r="B93" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10072,19 +10068,23 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591829</v>
+        <v>591938</v>
       </c>
       <c r="R93" t="n">
-        <v>6985164</v>
+        <v>6985274</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10154,7 +10154,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431303</v>
+        <v>129431292</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591852</v>
+        <v>591779</v>
       </c>
       <c r="R94" t="n">
-        <v>6985216</v>
+        <v>6985266</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10224,12 +10224,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10256,7 +10256,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431292</v>
+        <v>129431300</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10285,21 +10285,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591779</v>
+        <v>591764</v>
       </c>
       <c r="R95" t="n">
-        <v>6985266</v>
+        <v>6985160</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10332,6 +10335,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10358,7 +10366,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431300</v>
+        <v>129431303</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10387,24 +10395,21 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591764</v>
+        <v>591852</v>
       </c>
       <c r="R96" t="n">
-        <v>6985160</v>
+        <v>6985216</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10431,17 +10436,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,42 +10479,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R97" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10573,10 +10565,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10584,34 +10576,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R98" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129431299</v>
+        <v>129431354</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,39 +11277,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>591817</v>
+        <v>591920</v>
       </c>
       <c r="R105" t="n">
-        <v>6985225</v>
+        <v>6985069</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11336,12 +11331,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11465,10 +11460,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431354</v>
+        <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11476,34 +11471,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591920</v>
+        <v>591817</v>
       </c>
       <c r="R107" t="n">
-        <v>6985069</v>
+        <v>6985225</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11951,34 +11951,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B112" t="n">
-        <v>80178</v>
+        <v>91573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11986,10 +11982,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R112" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12048,30 +12044,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B113" t="n">
-        <v>91573</v>
+        <v>80178</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R113" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12238,57 +12238,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431355</v>
+        <v>129431334</v>
       </c>
       <c r="B115" t="n">
-        <v>57831</v>
+        <v>92148</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>760</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591975</v>
+        <v>592005</v>
       </c>
       <c r="R115" t="n">
-        <v>6985013</v>
+        <v>6985296</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12347,45 +12335,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431334</v>
+        <v>129431293</v>
       </c>
       <c r="B116" t="n">
-        <v>92148</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>592005</v>
+        <v>591777</v>
       </c>
       <c r="R116" t="n">
-        <v>6985296</v>
+        <v>6985297</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12412,12 +12405,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12444,7 +12437,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431293</v>
+        <v>129431298</v>
       </c>
       <c r="B117" t="n">
         <v>57727</v>
@@ -12484,10 +12477,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591777</v>
+        <v>591793</v>
       </c>
       <c r="R117" t="n">
-        <v>6985297</v>
+        <v>6985264</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12546,27 +12539,27 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431298</v>
+        <v>129431355</v>
       </c>
       <c r="B118" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12574,22 +12567,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591793</v>
+        <v>591975</v>
       </c>
       <c r="R118" t="n">
-        <v>6985264</v>
+        <v>6985013</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12616,12 +12616,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9258,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129431350</v>
+        <v>129431351</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,21 +9269,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>591921</v>
+        <v>591924</v>
       </c>
       <c r="R85" t="n">
-        <v>6985249</v>
+        <v>6985247</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129431351</v>
+        <v>129431350</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>591924</v>
+        <v>591921</v>
       </c>
       <c r="R86" t="n">
-        <v>6985247</v>
+        <v>6985249</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431341</v>
+        <v>129431300</v>
       </c>
       <c r="B92" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,30 +9975,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591829</v>
+        <v>591764</v>
       </c>
       <c r="R92" t="n">
-        <v>6985164</v>
+        <v>6985160</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10025,12 +10037,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10057,10 +10074,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431335</v>
+        <v>129431292</v>
       </c>
       <c r="B93" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10068,34 +10085,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591938</v>
+        <v>591779</v>
       </c>
       <c r="R93" t="n">
-        <v>6985274</v>
+        <v>6985266</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10122,12 +10144,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10154,7 +10176,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431292</v>
+        <v>129431303</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10194,10 +10216,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591779</v>
+        <v>591852</v>
       </c>
       <c r="R94" t="n">
-        <v>6985266</v>
+        <v>6985216</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10224,12 +10246,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10256,10 +10278,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431300</v>
+        <v>129431335</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10267,42 +10289,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591764</v>
+        <v>591938</v>
       </c>
       <c r="R95" t="n">
-        <v>6985160</v>
+        <v>6985274</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10329,17 +10343,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10366,10 +10375,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431303</v>
+        <v>129431341</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10377,39 +10386,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591852</v>
+        <v>591829</v>
       </c>
       <c r="R96" t="n">
-        <v>6985216</v>
+        <v>6985164</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B97" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,34 +10479,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R97" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10565,10 +10573,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10576,42 +10584,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R98" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11363,45 +11363,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431338</v>
+        <v>129431299</v>
       </c>
       <c r="B106" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591805</v>
+        <v>591817</v>
       </c>
       <c r="R106" t="n">
-        <v>6985202</v>
+        <v>6985225</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11428,12 +11433,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11460,50 +11465,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431299</v>
+        <v>129431338</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591817</v>
+        <v>591805</v>
       </c>
       <c r="R107" t="n">
-        <v>6985225</v>
+        <v>6985202</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12141,32 +12141,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431339</v>
+        <v>129431334</v>
       </c>
       <c r="B114" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12176,10 +12176,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591807</v>
+        <v>592005</v>
       </c>
       <c r="R114" t="n">
-        <v>6985203</v>
+        <v>6985296</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12238,32 +12238,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431334</v>
+        <v>129431339</v>
       </c>
       <c r="B115" t="n">
-        <v>92148</v>
+        <v>80149</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12273,10 +12273,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>592005</v>
+        <v>591807</v>
       </c>
       <c r="R115" t="n">
-        <v>6985296</v>
+        <v>6985203</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9258,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129431351</v>
+        <v>129431350</v>
       </c>
       <c r="B85" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,21 +9269,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>591924</v>
+        <v>591921</v>
       </c>
       <c r="R85" t="n">
-        <v>6985247</v>
+        <v>6985249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129431350</v>
+        <v>129431351</v>
       </c>
       <c r="B86" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>591921</v>
+        <v>591924</v>
       </c>
       <c r="R86" t="n">
-        <v>6985249</v>
+        <v>6985247</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431300</v>
+        <v>129431341</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,42 +9975,30 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591764</v>
+        <v>591829</v>
       </c>
       <c r="R92" t="n">
-        <v>6985160</v>
+        <v>6985164</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10037,17 +10025,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10074,10 +10057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431292</v>
+        <v>129431335</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10085,39 +10068,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591779</v>
+        <v>591938</v>
       </c>
       <c r="R93" t="n">
-        <v>6985266</v>
+        <v>6985274</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10144,12 +10122,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10176,7 +10154,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431303</v>
+        <v>129431292</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10216,10 +10194,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591852</v>
+        <v>591779</v>
       </c>
       <c r="R94" t="n">
-        <v>6985216</v>
+        <v>6985266</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10246,12 +10224,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10278,10 +10256,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431335</v>
+        <v>129431300</v>
       </c>
       <c r="B95" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10289,34 +10267,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591938</v>
+        <v>591764</v>
       </c>
       <c r="R95" t="n">
-        <v>6985274</v>
+        <v>6985160</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10343,12 +10329,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10375,10 +10366,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431341</v>
+        <v>129431303</v>
       </c>
       <c r="B96" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10386,30 +10377,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591829</v>
+        <v>591852</v>
       </c>
       <c r="R96" t="n">
-        <v>6985164</v>
+        <v>6985216</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,42 +10479,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R97" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10573,10 +10565,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10584,34 +10576,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R98" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11363,50 +11363,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129431299</v>
+        <v>129431338</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>591817</v>
+        <v>591805</v>
       </c>
       <c r="R106" t="n">
-        <v>6985225</v>
+        <v>6985202</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11433,12 +11428,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11465,45 +11460,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129431338</v>
+        <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>591805</v>
+        <v>591817</v>
       </c>
       <c r="R107" t="n">
-        <v>6985202</v>
+        <v>6985225</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12141,45 +12141,57 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431334</v>
+        <v>129431355</v>
       </c>
       <c r="B114" t="n">
-        <v>92148</v>
+        <v>57831</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>592005</v>
+        <v>591975</v>
       </c>
       <c r="R114" t="n">
-        <v>6985296</v>
+        <v>6985013</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12238,32 +12250,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431339</v>
+        <v>129431334</v>
       </c>
       <c r="B115" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12273,10 +12285,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591807</v>
+        <v>592005</v>
       </c>
       <c r="R115" t="n">
-        <v>6985203</v>
+        <v>6985296</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12335,10 +12347,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431293</v>
+        <v>129431339</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12346,39 +12358,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591777</v>
+        <v>591807</v>
       </c>
       <c r="R116" t="n">
-        <v>6985297</v>
+        <v>6985203</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12405,12 +12412,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12437,7 +12444,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431298</v>
+        <v>129431293</v>
       </c>
       <c r="B117" t="n">
         <v>57727</v>
@@ -12477,10 +12484,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591793</v>
+        <v>591777</v>
       </c>
       <c r="R117" t="n">
-        <v>6985264</v>
+        <v>6985297</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12539,27 +12546,27 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431355</v>
+        <v>129431298</v>
       </c>
       <c r="B118" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12567,29 +12574,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591975</v>
+        <v>591793</v>
       </c>
       <c r="R118" t="n">
-        <v>6985013</v>
+        <v>6985264</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12616,12 +12616,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9452,7 +9452,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129431295</v>
+        <v>129431307</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9481,21 +9481,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>591845</v>
+        <v>591866</v>
       </c>
       <c r="R87" t="n">
-        <v>6985340</v>
+        <v>6985144</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9522,12 +9525,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9554,7 +9557,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129431307</v>
+        <v>129431295</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9583,24 +9586,21 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>591866</v>
+        <v>591845</v>
       </c>
       <c r="R88" t="n">
-        <v>6985144</v>
+        <v>6985340</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9964,10 +9964,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129431341</v>
+        <v>129431335</v>
       </c>
       <c r="B92" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,19 +9975,23 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9995,10 +9999,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>591829</v>
+        <v>591938</v>
       </c>
       <c r="R92" t="n">
-        <v>6985164</v>
+        <v>6985274</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10057,10 +10061,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431335</v>
+        <v>129431303</v>
       </c>
       <c r="B93" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10068,34 +10072,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591938</v>
+        <v>591852</v>
       </c>
       <c r="R93" t="n">
-        <v>6985274</v>
+        <v>6985216</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10366,10 +10375,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431303</v>
+        <v>129431341</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10377,39 +10386,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591852</v>
+        <v>591829</v>
       </c>
       <c r="R96" t="n">
-        <v>6985216</v>
+        <v>6985164</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B97" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,34 +10479,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R97" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10565,10 +10573,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10576,42 +10584,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R98" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B109" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,19 +11670,23 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R109" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11752,10 +11756,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B110" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11763,23 +11767,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R110" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11951,30 +11951,34 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B112" t="n">
-        <v>91573</v>
+        <v>80178</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11982,10 +11986,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R112" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12044,34 +12048,30 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B113" t="n">
-        <v>80178</v>
+        <v>91573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R113" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12141,57 +12141,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431355</v>
+        <v>129431339</v>
       </c>
       <c r="B114" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591975</v>
+        <v>591807</v>
       </c>
       <c r="R114" t="n">
-        <v>6985013</v>
+        <v>6985203</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12347,10 +12335,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431339</v>
+        <v>129431293</v>
       </c>
       <c r="B116" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12358,34 +12346,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591807</v>
+        <v>591777</v>
       </c>
       <c r="R116" t="n">
-        <v>6985203</v>
+        <v>6985297</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12412,12 +12405,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12444,7 +12437,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431293</v>
+        <v>129431298</v>
       </c>
       <c r="B117" t="n">
         <v>57727</v>
@@ -12484,10 +12477,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591777</v>
+        <v>591793</v>
       </c>
       <c r="R117" t="n">
-        <v>6985297</v>
+        <v>6985264</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12546,27 +12539,27 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431298</v>
+        <v>129431355</v>
       </c>
       <c r="B118" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12574,22 +12567,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591793</v>
+        <v>591975</v>
       </c>
       <c r="R118" t="n">
-        <v>6985264</v>
+        <v>6985013</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12616,12 +12616,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9258,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129431350</v>
+        <v>129431351</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,21 +9269,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>591921</v>
+        <v>591924</v>
       </c>
       <c r="R85" t="n">
-        <v>6985249</v>
+        <v>6985247</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129431351</v>
+        <v>129431350</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>591924</v>
+        <v>591921</v>
       </c>
       <c r="R86" t="n">
-        <v>6985247</v>
+        <v>6985249</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129431307</v>
+        <v>129431295</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9481,24 +9481,21 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>591866</v>
+        <v>591845</v>
       </c>
       <c r="R87" t="n">
-        <v>6985144</v>
+        <v>6985340</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9525,12 +9522,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9557,7 +9554,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129431295</v>
+        <v>129431307</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9586,21 +9583,24 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>591845</v>
+        <v>591866</v>
       </c>
       <c r="R88" t="n">
-        <v>6985340</v>
+        <v>6985144</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10061,7 +10061,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431303</v>
+        <v>129431300</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -10090,21 +10090,24 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591852</v>
+        <v>591764</v>
       </c>
       <c r="R93" t="n">
-        <v>6985216</v>
+        <v>6985160</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10131,12 +10134,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10163,10 +10171,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431292</v>
+        <v>129431341</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10174,39 +10182,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591779</v>
+        <v>591829</v>
       </c>
       <c r="R94" t="n">
-        <v>6985266</v>
+        <v>6985164</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10233,12 +10232,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10265,7 +10264,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431300</v>
+        <v>129431292</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10294,24 +10293,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591764</v>
+        <v>591779</v>
       </c>
       <c r="R95" t="n">
-        <v>6985160</v>
+        <v>6985266</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10344,11 +10340,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10375,10 +10366,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431341</v>
+        <v>129431303</v>
       </c>
       <c r="B96" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10386,30 +10377,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591829</v>
+        <v>591852</v>
       </c>
       <c r="R96" t="n">
-        <v>6985164</v>
+        <v>6985216</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B99" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,19 +10681,23 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10701,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R99" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10763,10 +10767,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B100" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10774,23 +10778,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R100" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12238,45 +12238,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431334</v>
+        <v>129431293</v>
       </c>
       <c r="B115" t="n">
-        <v>92148</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>592005</v>
+        <v>591777</v>
       </c>
       <c r="R115" t="n">
-        <v>6985296</v>
+        <v>6985297</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12303,12 +12308,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12335,7 +12340,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431293</v>
+        <v>129431298</v>
       </c>
       <c r="B116" t="n">
         <v>57727</v>
@@ -12375,10 +12380,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591777</v>
+        <v>591793</v>
       </c>
       <c r="R116" t="n">
-        <v>6985297</v>
+        <v>6985264</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12437,27 +12442,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129431298</v>
+        <v>129431355</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12465,22 +12470,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>591793</v>
+        <v>591975</v>
       </c>
       <c r="R117" t="n">
-        <v>6985264</v>
+        <v>6985013</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12507,12 +12519,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12539,57 +12551,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431355</v>
+        <v>129431334</v>
       </c>
       <c r="B118" t="n">
-        <v>57831</v>
+        <v>92148</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103031</v>
+        <v>760</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>591975</v>
+        <v>592005</v>
       </c>
       <c r="R118" t="n">
-        <v>6985013</v>
+        <v>6985296</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>

--- a/artfynd/A 48264-2024 artfynd.xlsx
+++ b/artfynd/A 48264-2024 artfynd.xlsx
@@ -9258,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129431351</v>
+        <v>129431350</v>
       </c>
       <c r="B85" t="n">
-        <v>80149</v>
+        <v>80176</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,21 +9269,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>591924</v>
+        <v>591921</v>
       </c>
       <c r="R85" t="n">
-        <v>6985247</v>
+        <v>6985249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129431350</v>
+        <v>129431351</v>
       </c>
       <c r="B86" t="n">
-        <v>80150</v>
+        <v>80175</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>591921</v>
+        <v>591924</v>
       </c>
       <c r="R86" t="n">
-        <v>6985249</v>
+        <v>6985247</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9455,7 +9455,7 @@
         <v>129431295</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>129431307</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>129431297</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>129431301</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>129431352</v>
       </c>
       <c r="B91" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>129431335</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10061,10 +10061,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129431300</v>
+        <v>129431292</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10090,24 +10090,21 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>591764</v>
+        <v>591779</v>
       </c>
       <c r="R93" t="n">
-        <v>6985160</v>
+        <v>6985266</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10140,11 +10137,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10171,10 +10163,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129431341</v>
+        <v>129431300</v>
       </c>
       <c r="B94" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10182,30 +10174,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>591829</v>
+        <v>591764</v>
       </c>
       <c r="R94" t="n">
-        <v>6985164</v>
+        <v>6985160</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10232,12 +10236,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack, troligen ifrån i våras.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10264,10 +10273,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129431292</v>
+        <v>129431303</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10304,10 +10313,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>591779</v>
+        <v>591852</v>
       </c>
       <c r="R95" t="n">
-        <v>6985266</v>
+        <v>6985216</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10334,12 +10343,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10366,10 +10375,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129431303</v>
+        <v>129431341</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10377,39 +10386,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>591852</v>
+        <v>591829</v>
       </c>
       <c r="R96" t="n">
-        <v>6985216</v>
+        <v>6985164</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129431340</v>
+        <v>129431347</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>80175</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10479,42 +10479,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>591826</v>
+        <v>591979</v>
       </c>
       <c r="R97" t="n">
-        <v>6985197</v>
+        <v>6985182</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10573,10 +10565,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129431347</v>
+        <v>129431340</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10584,34 +10576,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>591979</v>
+        <v>591826</v>
       </c>
       <c r="R98" t="n">
-        <v>6985182</v>
+        <v>6985197</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129431349</v>
+        <v>129431345</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>91601</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,23 +10681,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10705,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>591958</v>
+        <v>591986</v>
       </c>
       <c r="R99" t="n">
-        <v>6985180</v>
+        <v>6985193</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10767,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129431345</v>
+        <v>129431349</v>
       </c>
       <c r="B100" t="n">
-        <v>91573</v>
+        <v>80175</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,19 +10774,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>591986</v>
+        <v>591958</v>
       </c>
       <c r="R100" t="n">
-        <v>6985193</v>
+        <v>6985180</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10863,7 +10863,7 @@
         <v>129431346</v>
       </c>
       <c r="B101" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>129431296</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>129431304</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>129431294</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>129431354</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>129431338</v>
       </c>
       <c r="B106" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>129431299</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>129431336</v>
       </c>
       <c r="B108" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11659,10 +11659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129431344</v>
+        <v>129431337</v>
       </c>
       <c r="B109" t="n">
-        <v>80149</v>
+        <v>91601</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11670,23 +11670,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11694,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>592011</v>
+        <v>591849</v>
       </c>
       <c r="R109" t="n">
-        <v>6985171</v>
+        <v>6985248</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11756,10 +11752,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129431337</v>
+        <v>129431344</v>
       </c>
       <c r="B110" t="n">
-        <v>91573</v>
+        <v>80175</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11767,19 +11763,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>591849</v>
+        <v>592011</v>
       </c>
       <c r="R110" t="n">
-        <v>6985248</v>
+        <v>6985171</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11852,7 +11852,7 @@
         <v>129431302</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,34 +11951,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129431348</v>
+        <v>129431353</v>
       </c>
       <c r="B112" t="n">
-        <v>80178</v>
+        <v>91601</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11986,10 +11982,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>591980</v>
+        <v>591892</v>
       </c>
       <c r="R112" t="n">
-        <v>6985185</v>
+        <v>6985085</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12048,30 +12044,34 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129431353</v>
+        <v>129431348</v>
       </c>
       <c r="B113" t="n">
-        <v>91573</v>
+        <v>80204</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>591892</v>
+        <v>591980</v>
       </c>
       <c r="R113" t="n">
-        <v>6985085</v>
+        <v>6985185</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12141,10 +12141,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129431339</v>
+        <v>129431293</v>
       </c>
       <c r="B114" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12152,34 +12152,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>591807</v>
+        <v>591777</v>
       </c>
       <c r="R114" t="n">
-        <v>6985203</v>
+        <v>6985297</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12206,12 +12211,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12238,10 +12243,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129431293</v>
+        <v>129431298</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12278,10 +12283,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>591777</v>
+        <v>591793</v>
       </c>
       <c r="R115" t="n">
-        <v>6985297</v>
+        <v>6985264</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12340,50 +12345,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129431298</v>
+        <v>129431334</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>92176</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>591793</v>
+        <v>592005</v>
       </c>
       <c r="R116" t="n">
-        <v>6985264</v>
+        <v>6985296</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12410,12 +12410,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12445,7 +12445,7 @@
         <v>129431355</v>
       </c>
       <c r="B117" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12551,32 +12551,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129431334</v>
+        <v>129431339</v>
       </c>
       <c r="B118" t="n">
-        <v>92148</v>
+        <v>80175</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>592005</v>
+        <v>591807</v>
       </c>
       <c r="R118" t="n">
-        <v>6985296</v>
+        <v>6985203</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
